--- a/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
   <si>
     <t>RERE</t>
   </si>
@@ -656,250 +656,275 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>409200</v>
+        <v>538500</v>
       </c>
       <c r="E8" s="3">
-        <v>396500</v>
+        <v>452800</v>
       </c>
       <c r="F8" s="3">
-        <v>411600</v>
+        <v>412000</v>
       </c>
       <c r="G8" s="3">
-        <v>350200</v>
+        <v>399200</v>
       </c>
       <c r="H8" s="3">
-        <v>296300</v>
+        <v>414400</v>
       </c>
       <c r="I8" s="3">
+        <v>352600</v>
+      </c>
+      <c r="J8" s="3">
+        <v>298300</v>
+      </c>
+      <c r="K8" s="3">
         <v>304700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>336300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>278900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>480800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>217500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>228900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>195400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>176200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>108400</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U8" s="3">
         <v>152300</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>358300</v>
+        <v>479800</v>
       </c>
       <c r="E9" s="3">
-        <v>347800</v>
+        <v>403000</v>
       </c>
       <c r="F9" s="3">
-        <v>365300</v>
+        <v>360700</v>
       </c>
       <c r="G9" s="3">
-        <v>305100</v>
+        <v>350100</v>
       </c>
       <c r="H9" s="3">
-        <v>266400</v>
+        <v>367800</v>
       </c>
       <c r="I9" s="3">
+        <v>307100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>268200</v>
+      </c>
+      <c r="K9" s="3">
         <v>267400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>288700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>244100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>425000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>189400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>198600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>169900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>153100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>103100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>590400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>149000</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>51000</v>
+        <v>58700</v>
       </c>
       <c r="E10" s="3">
-        <v>48800</v>
+        <v>49800</v>
       </c>
       <c r="F10" s="3">
-        <v>46400</v>
+        <v>51300</v>
       </c>
       <c r="G10" s="3">
-        <v>45100</v>
+        <v>49100</v>
       </c>
       <c r="H10" s="3">
-        <v>29900</v>
+        <v>46700</v>
       </c>
       <c r="I10" s="3">
+        <v>45400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>30100</v>
+      </c>
+      <c r="K10" s="3">
         <v>37300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>47700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>34800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>55800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>28100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>30300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>25500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>23100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>5200</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U10" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,61 +944,69 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F12" s="3">
         <v>6200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>6500</v>
       </c>
-      <c r="F12" s="3">
-        <v>7500</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I12" s="3">
         <v>6700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K12" s="3">
+        <v>8600</v>
+      </c>
+      <c r="L12" s="3">
+        <v>8600</v>
+      </c>
+      <c r="M12" s="3">
+        <v>9000</v>
+      </c>
+      <c r="N12" s="3">
+        <v>19100</v>
+      </c>
+      <c r="O12" s="3">
         <v>8000</v>
       </c>
-      <c r="I12" s="3">
-        <v>8600</v>
-      </c>
-      <c r="J12" s="3">
-        <v>8600</v>
-      </c>
-      <c r="K12" s="3">
-        <v>9000</v>
-      </c>
-      <c r="L12" s="3">
-        <v>19100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>8000</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>5500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>5600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>4900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>6300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>22000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,38 +1058,44 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>253000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>254700</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>2300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1069,53 +1108,59 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F15" s="3">
         <v>10800</v>
       </c>
-      <c r="E15" s="3">
-        <v>10900</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G15" s="3">
-        <v>12200</v>
-      </c>
-      <c r="H15" s="3">
-        <v>12800</v>
+        <v>11000</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="J15" s="3">
+        <v>12900</v>
+      </c>
+      <c r="K15" s="3">
         <v>12100</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3">
         <v>13000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>22100</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1131,8 +1176,14 @@
       <c r="S15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1200,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>417600</v>
+      <c r="D17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E17" s="3">
-        <v>405900</v>
+        <v>456700</v>
       </c>
       <c r="F17" s="3">
-        <v>718600</v>
+        <v>420500</v>
       </c>
       <c r="G17" s="3">
-        <v>365400</v>
+        <v>408600</v>
       </c>
       <c r="H17" s="3">
-        <v>319500</v>
+        <v>723500</v>
       </c>
       <c r="I17" s="3">
+        <v>367900</v>
+      </c>
+      <c r="J17" s="3">
+        <v>321700</v>
+      </c>
+      <c r="K17" s="3">
         <v>323300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>356000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>300300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>568700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>233500</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3">
         <v>139500</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-8400</v>
+      <c r="D18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>-9300</v>
+        <v>-3900</v>
       </c>
       <c r="F18" s="3">
-        <v>-306900</v>
+        <v>-8500</v>
       </c>
       <c r="G18" s="3">
-        <v>-15200</v>
+        <v>-9400</v>
       </c>
       <c r="H18" s="3">
-        <v>-23200</v>
+        <v>-309000</v>
       </c>
       <c r="I18" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-18600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-19700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-21400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-88000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-16000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3">
         <v>-31100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,61 +1341,69 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
+        <v>900</v>
+      </c>
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>9600</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>9700</v>
+      </c>
+      <c r="J20" s="3">
         <v>4800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-5100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-4800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3">
         <v>1300</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1352,197 +1425,221 @@
       <c r="I21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3">
         <v>27200</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>-2900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
         <v>-15100</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
+        <v>300</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>1700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>600</v>
-      </c>
-      <c r="R22" s="3">
-        <v>1900</v>
       </c>
       <c r="S22" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U22" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-8200</v>
+        <v>-600</v>
       </c>
       <c r="E23" s="3">
-        <v>-8400</v>
+        <v>-3300</v>
       </c>
       <c r="F23" s="3">
-        <v>-306900</v>
+        <v>-8300</v>
       </c>
       <c r="G23" s="3">
-        <v>-5800</v>
+        <v>-8500</v>
       </c>
       <c r="H23" s="3">
-        <v>-18800</v>
+        <v>-309000</v>
       </c>
       <c r="I23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-23800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-24700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-20600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-89600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-16300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-13100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-15400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-30400</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U23" s="3">
         <v>-40800</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F24" s="3">
         <v>-1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-1600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-9900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="K24" s="3">
         <v>-1800</v>
       </c>
-      <c r="H24" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="L24" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="M24" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="N24" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="O24" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="P24" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="R24" s="3">
         <v>-1800</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-11300</v>
-      </c>
-      <c r="K24" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="L24" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="R24" s="3">
-        <v>-4600</v>
       </c>
       <c r="S24" s="3">
         <v>-1900</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="U24" s="3">
+        <v>-1900</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1691,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-6600</v>
+      <c r="D26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="G26" s="3">
         <v>-6800</v>
       </c>
-      <c r="F26" s="3">
-        <v>-297000</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-299000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-4000</v>
       </c>
-      <c r="H26" s="3">
-        <v>-16900</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="K26" s="3">
         <v>-22000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-13400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-17300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-84100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-13500</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3">
         <v>-28500</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-9000</v>
       </c>
-      <c r="E27" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-297000</v>
-      </c>
       <c r="G27" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-299100</v>
+      </c>
+      <c r="I27" s="3">
         <v>-4200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="M27" s="3">
         <v>-17300</v>
       </c>
-      <c r="I27" s="3">
-        <v>-22300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-14300</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-17300</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-156300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-86700</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3">
         <v>-80200</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1868,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1927,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1986,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +2045,132 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="J32" s="3">
         <v>-4800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>5100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>4800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3">
         <v>-1300</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-9000</v>
       </c>
-      <c r="E33" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-297000</v>
-      </c>
       <c r="G33" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-299100</v>
+      </c>
+      <c r="I33" s="3">
         <v>-4200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="M33" s="3">
         <v>-17300</v>
       </c>
-      <c r="I33" s="3">
-        <v>-22300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-14300</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-17300</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-156300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-86700</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3">
         <v>-80200</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2222,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-9000</v>
       </c>
-      <c r="E35" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-297000</v>
-      </c>
       <c r="G35" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-299100</v>
+      </c>
+      <c r="I35" s="3">
         <v>-4200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="M35" s="3">
         <v>-17300</v>
       </c>
-      <c r="I35" s="3">
-        <v>-22300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-14300</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-17300</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-156300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-86700</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3">
         <v>-80200</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2372,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,47 +2395,49 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>206100</v>
+        <v>275100</v>
       </c>
       <c r="E41" s="3">
-        <v>216200</v>
+        <v>199100</v>
       </c>
       <c r="F41" s="3">
-        <v>235200</v>
+        <v>207500</v>
       </c>
       <c r="G41" s="3">
-        <v>175400</v>
+        <v>217700</v>
       </c>
       <c r="H41" s="3">
-        <v>167900</v>
+        <v>236800</v>
       </c>
       <c r="I41" s="3">
+        <v>176600</v>
+      </c>
+      <c r="J41" s="3">
+        <v>169000</v>
+      </c>
+      <c r="K41" s="3">
         <v>155500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>187300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>269500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>396000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>94400</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2277,46 +2450,52 @@
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>82700</v>
+        <v>57100</v>
       </c>
       <c r="E42" s="3">
-        <v>89000</v>
+        <v>48400</v>
       </c>
       <c r="F42" s="3">
-        <v>108000</v>
+        <v>83300</v>
       </c>
       <c r="G42" s="3">
-        <v>139900</v>
+        <v>89600</v>
       </c>
       <c r="H42" s="3">
-        <v>142300</v>
+        <v>108700</v>
       </c>
       <c r="I42" s="3">
+        <v>140800</v>
+      </c>
+      <c r="J42" s="3">
+        <v>143300</v>
+      </c>
+      <c r="K42" s="3">
         <v>121500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>70500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>54000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>7100</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>4</v>
@@ -2330,47 +2509,53 @@
       <c r="S42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>56500</v>
+        <v>47600</v>
       </c>
       <c r="E43" s="3">
-        <v>54600</v>
+        <v>77200</v>
       </c>
       <c r="F43" s="3">
-        <v>94200</v>
+        <v>56900</v>
       </c>
       <c r="G43" s="3">
-        <v>71100</v>
+        <v>55000</v>
       </c>
       <c r="H43" s="3">
-        <v>67200</v>
+        <v>94800</v>
       </c>
       <c r="I43" s="3">
+        <v>71600</v>
+      </c>
+      <c r="J43" s="3">
+        <v>67600</v>
+      </c>
+      <c r="K43" s="3">
         <v>99100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>112600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>83400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>70600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>65800</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2383,47 +2568,53 @@
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>101500</v>
+        <v>141400</v>
       </c>
       <c r="E44" s="3">
-        <v>80600</v>
+        <v>93500</v>
       </c>
       <c r="F44" s="3">
-        <v>59900</v>
+        <v>102200</v>
       </c>
       <c r="G44" s="3">
-        <v>62700</v>
+        <v>81100</v>
       </c>
       <c r="H44" s="3">
-        <v>93000</v>
+        <v>60300</v>
       </c>
       <c r="I44" s="3">
+        <v>63100</v>
+      </c>
+      <c r="J44" s="3">
+        <v>93600</v>
+      </c>
+      <c r="K44" s="3">
         <v>92200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>66100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>71100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>50100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>45600</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2436,47 +2627,53 @@
       <c r="S44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>93600</v>
+        <v>108100</v>
       </c>
       <c r="E45" s="3">
-        <v>84000</v>
+        <v>113100</v>
       </c>
       <c r="F45" s="3">
-        <v>39900</v>
+        <v>94300</v>
       </c>
       <c r="G45" s="3">
-        <v>95300</v>
+        <v>84500</v>
       </c>
       <c r="H45" s="3">
-        <v>96300</v>
+        <v>40200</v>
       </c>
       <c r="I45" s="3">
+        <v>96000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>96900</v>
+      </c>
+      <c r="K45" s="3">
         <v>107300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>136700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>117000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>79900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>63100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2489,47 +2686,53 @@
       <c r="S45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>540500</v>
+        <v>629300</v>
       </c>
       <c r="E46" s="3">
-        <v>524300</v>
+        <v>531300</v>
       </c>
       <c r="F46" s="3">
-        <v>537200</v>
+        <v>544200</v>
       </c>
       <c r="G46" s="3">
-        <v>544400</v>
+        <v>527800</v>
       </c>
       <c r="H46" s="3">
-        <v>566700</v>
+        <v>540800</v>
       </c>
       <c r="I46" s="3">
+        <v>548100</v>
+      </c>
+      <c r="J46" s="3">
+        <v>570500</v>
+      </c>
+      <c r="K46" s="3">
         <v>575700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>573100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>595100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>603700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>268800</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2542,47 +2745,53 @@
       <c r="S46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>67000</v>
+        <v>64900</v>
       </c>
       <c r="E47" s="3">
-        <v>68100</v>
+        <v>65200</v>
       </c>
       <c r="F47" s="3">
-        <v>30300</v>
+        <v>67500</v>
       </c>
       <c r="G47" s="3">
-        <v>31700</v>
+        <v>68600</v>
       </c>
       <c r="H47" s="3">
-        <v>32400</v>
+        <v>30500</v>
       </c>
       <c r="I47" s="3">
+        <v>31900</v>
+      </c>
+      <c r="J47" s="3">
+        <v>32600</v>
+      </c>
+      <c r="K47" s="3">
         <v>32800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>33400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>29200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>16200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>15100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2595,47 +2804,53 @@
       <c r="S47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>16700</v>
+        <v>20600</v>
       </c>
       <c r="E48" s="3">
-        <v>15400</v>
+        <v>18200</v>
       </c>
       <c r="F48" s="3">
-        <v>16400</v>
+        <v>16800</v>
       </c>
       <c r="G48" s="3">
-        <v>16300</v>
+        <v>15500</v>
       </c>
       <c r="H48" s="3">
-        <v>15900</v>
+        <v>16500</v>
       </c>
       <c r="I48" s="3">
+        <v>16500</v>
+      </c>
+      <c r="J48" s="3">
+        <v>16100</v>
+      </c>
+      <c r="K48" s="3">
         <v>14100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>14300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>12200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>11100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>9300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2648,47 +2863,53 @@
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>55800</v>
+        <v>37600</v>
       </c>
       <c r="E49" s="3">
-        <v>65500</v>
+        <v>46900</v>
       </c>
       <c r="F49" s="3">
-        <v>75200</v>
+        <v>56200</v>
       </c>
       <c r="G49" s="3">
-        <v>366300</v>
+        <v>66000</v>
       </c>
       <c r="H49" s="3">
-        <v>377500</v>
+        <v>75700</v>
       </c>
       <c r="I49" s="3">
+        <v>368800</v>
+      </c>
+      <c r="J49" s="3">
+        <v>380000</v>
+      </c>
+      <c r="K49" s="3">
         <v>386400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>397600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>421200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>432800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>444300</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2701,8 +2922,14 @@
       <c r="S49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2981,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,47 +3040,53 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>11400</v>
+        <v>11200</v>
       </c>
       <c r="E52" s="3">
-        <v>12100</v>
+        <v>10700</v>
       </c>
       <c r="F52" s="3">
-        <v>38100</v>
+        <v>11500</v>
       </c>
       <c r="G52" s="3">
-        <v>14300</v>
+        <v>12200</v>
       </c>
       <c r="H52" s="3">
-        <v>12600</v>
+        <v>38300</v>
       </c>
       <c r="I52" s="3">
+        <v>14400</v>
+      </c>
+      <c r="J52" s="3">
+        <v>12700</v>
+      </c>
+      <c r="K52" s="3">
         <v>14500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>17600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>20500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>13900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2400</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2860,8 +3099,14 @@
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,47 +3158,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>691500</v>
+        <v>763600</v>
       </c>
       <c r="E54" s="3">
-        <v>685500</v>
+        <v>672400</v>
       </c>
       <c r="F54" s="3">
-        <v>697100</v>
+        <v>696200</v>
       </c>
       <c r="G54" s="3">
-        <v>973000</v>
+        <v>690100</v>
       </c>
       <c r="H54" s="3">
-        <v>1005000</v>
+        <v>701900</v>
       </c>
       <c r="I54" s="3">
+        <v>979600</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1011900</v>
+      </c>
+      <c r="K54" s="3">
         <v>1023500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1036000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1078300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1077800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>739900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2966,8 +3217,14 @@
       <c r="S54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3244,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,47 +3267,49 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9700</v>
+        <v>74000</v>
       </c>
       <c r="E57" s="3">
-        <v>11700</v>
+        <v>16200</v>
       </c>
       <c r="F57" s="3">
-        <v>10100</v>
+        <v>9800</v>
       </c>
       <c r="G57" s="3">
-        <v>7800</v>
+        <v>11800</v>
       </c>
       <c r="H57" s="3">
-        <v>9200</v>
+        <v>10200</v>
       </c>
       <c r="I57" s="3">
+        <v>7900</v>
+      </c>
+      <c r="J57" s="3">
+        <v>9300</v>
+      </c>
+      <c r="K57" s="3">
         <v>10400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>7000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>6900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>6300</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3061,47 +3322,53 @@
       <c r="S57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>38500</v>
+        <v>48600</v>
       </c>
       <c r="E58" s="3">
-        <v>44000</v>
+        <v>27800</v>
       </c>
       <c r="F58" s="3">
-        <v>17100</v>
+        <v>38800</v>
       </c>
       <c r="G58" s="3">
+        <v>44300</v>
+      </c>
+      <c r="H58" s="3">
+        <v>17200</v>
+      </c>
+      <c r="I58" s="3">
         <v>10500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
+        <v>20300</v>
+      </c>
+      <c r="K58" s="3">
+        <v>21300</v>
+      </c>
+      <c r="L58" s="3">
+        <v>13100</v>
+      </c>
+      <c r="M58" s="3">
         <v>20200</v>
       </c>
-      <c r="I58" s="3">
-        <v>21300</v>
-      </c>
-      <c r="J58" s="3">
-        <v>13100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>20200</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>29700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>63500</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3114,47 +3381,53 @@
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>106500</v>
+        <v>112500</v>
       </c>
       <c r="E59" s="3">
-        <v>84400</v>
+        <v>94600</v>
       </c>
       <c r="F59" s="3">
-        <v>113900</v>
+        <v>107200</v>
       </c>
       <c r="G59" s="3">
-        <v>99400</v>
+        <v>85000</v>
       </c>
       <c r="H59" s="3">
-        <v>114000</v>
+        <v>114700</v>
       </c>
       <c r="I59" s="3">
+        <v>100100</v>
+      </c>
+      <c r="J59" s="3">
+        <v>114800</v>
+      </c>
+      <c r="K59" s="3">
         <v>106100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>95000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>83000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>77700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>85300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3167,47 +3440,53 @@
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>154800</v>
+        <v>235100</v>
       </c>
       <c r="E60" s="3">
-        <v>140200</v>
+        <v>138600</v>
       </c>
       <c r="F60" s="3">
-        <v>141200</v>
+        <v>155800</v>
       </c>
       <c r="G60" s="3">
-        <v>117700</v>
+        <v>141100</v>
       </c>
       <c r="H60" s="3">
-        <v>143400</v>
+        <v>142100</v>
       </c>
       <c r="I60" s="3">
+        <v>118500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>144400</v>
+      </c>
+      <c r="K60" s="3">
         <v>137800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>113900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>110100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>114300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>155100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3220,8 +3499,14 @@
       <c r="S60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3247,20 +3532,20 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3273,47 +3558,53 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>14600</v>
+        <v>12500</v>
       </c>
       <c r="E62" s="3">
-        <v>17000</v>
+        <v>13600</v>
       </c>
       <c r="F62" s="3">
-        <v>20000</v>
+        <v>14700</v>
       </c>
       <c r="G62" s="3">
-        <v>30600</v>
+        <v>17100</v>
       </c>
       <c r="H62" s="3">
-        <v>32200</v>
+        <v>20100</v>
       </c>
       <c r="I62" s="3">
+        <v>30800</v>
+      </c>
+      <c r="J62" s="3">
+        <v>32400</v>
+      </c>
+      <c r="K62" s="3">
         <v>33900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>35600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>46600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>52600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>46300</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3326,8 +3617,14 @@
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3676,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3735,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,47 +3794,53 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>169300</v>
+        <v>247700</v>
       </c>
       <c r="E66" s="3">
-        <v>157200</v>
+        <v>152200</v>
       </c>
       <c r="F66" s="3">
-        <v>161200</v>
+        <v>170500</v>
       </c>
       <c r="G66" s="3">
-        <v>148300</v>
+        <v>158200</v>
       </c>
       <c r="H66" s="3">
-        <v>175600</v>
+        <v>162200</v>
       </c>
       <c r="I66" s="3">
+        <v>149300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>176800</v>
+      </c>
+      <c r="K66" s="3">
         <v>171700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>149400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>157500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>168900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>204600</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3538,8 +3853,14 @@
       <c r="S66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3880,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3935,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3994,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3698,14 +4033,14 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>1370500</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3718,8 +4053,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,8 +4112,14 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3782,36 +4129,36 @@
       <c r="E72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F72" s="3">
-        <v>-1243700</v>
+      <c r="F72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
+      <c r="H72" s="3">
+        <v>-1252100</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-902900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>-835500</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3824,8 +4171,14 @@
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4230,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4289,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,47 +4348,53 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>522200</v>
+        <v>516000</v>
       </c>
       <c r="E76" s="3">
-        <v>528300</v>
+        <v>520200</v>
       </c>
       <c r="F76" s="3">
-        <v>536000</v>
+        <v>525700</v>
       </c>
       <c r="G76" s="3">
-        <v>824700</v>
+        <v>531900</v>
       </c>
       <c r="H76" s="3">
-        <v>829400</v>
+        <v>539600</v>
       </c>
       <c r="I76" s="3">
+        <v>830300</v>
+      </c>
+      <c r="J76" s="3">
+        <v>835000</v>
+      </c>
+      <c r="K76" s="3">
         <v>851800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>886500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>920700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>908900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-835200</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4036,8 +4407,14 @@
       <c r="S76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4466,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-9000</v>
       </c>
-      <c r="E81" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-297000</v>
-      </c>
       <c r="G81" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-299100</v>
+      </c>
+      <c r="I81" s="3">
         <v>-4200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="M81" s="3">
         <v>-17300</v>
       </c>
-      <c r="I81" s="3">
-        <v>-22300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-14300</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-17300</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-156300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-86700</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3">
         <v>-80200</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,8 +4616,10 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4253,11 +4650,11 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>4</v>
@@ -4274,8 +4671,14 @@
       <c r="S83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4730,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4789,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4848,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4907,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,8 +4966,14 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4571,11 +5004,11 @@
       <c r="L89" s="3">
         <v>0</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>4</v>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>4</v>
@@ -4592,8 +5025,14 @@
       <c r="S89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,8 +5052,10 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4645,11 +5086,11 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>4</v>
@@ -4666,8 +5107,14 @@
       <c r="S91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +5166,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,8 +5225,14 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4804,11 +5263,11 @@
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>4</v>
@@ -4825,8 +5284,14 @@
       <c r="S94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5311,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4899,8 +5366,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5425,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5484,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,8 +5543,14 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5090,11 +5581,11 @@
       <c r="L100" s="3">
         <v>0</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>4</v>
@@ -5111,8 +5602,14 @@
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5143,11 +5640,11 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>4</v>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>4</v>
@@ -5164,8 +5661,14 @@
       <c r="S101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5196,11 +5699,11 @@
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>4</v>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>4</v>
@@ -5215,6 +5718,12 @@
         <v>4</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>RERE</t>
   </si>
@@ -656,275 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>538500</v>
+        <v>504400</v>
       </c>
       <c r="E8" s="3">
-        <v>452800</v>
+        <v>535200</v>
       </c>
       <c r="F8" s="3">
-        <v>412000</v>
+        <v>450000</v>
       </c>
       <c r="G8" s="3">
-        <v>399200</v>
+        <v>409500</v>
       </c>
       <c r="H8" s="3">
-        <v>414400</v>
+        <v>396800</v>
       </c>
       <c r="I8" s="3">
-        <v>352600</v>
+        <v>411900</v>
       </c>
       <c r="J8" s="3">
+        <v>350400</v>
+      </c>
+      <c r="K8" s="3">
         <v>298300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>304700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>336300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>278900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>480800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>217500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>228900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>195400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>176200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>108400</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3">
         <v>152300</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>479800</v>
+        <v>450100</v>
       </c>
       <c r="E9" s="3">
-        <v>403000</v>
+        <v>476800</v>
       </c>
       <c r="F9" s="3">
-        <v>360700</v>
+        <v>400500</v>
       </c>
       <c r="G9" s="3">
-        <v>350100</v>
+        <v>358500</v>
       </c>
       <c r="H9" s="3">
-        <v>367800</v>
+        <v>348000</v>
       </c>
       <c r="I9" s="3">
-        <v>307100</v>
+        <v>365500</v>
       </c>
       <c r="J9" s="3">
+        <v>305200</v>
+      </c>
+      <c r="K9" s="3">
         <v>268200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>267400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>288700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>244100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>425000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>189400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>198600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>169900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>153100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>103100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>590400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>149000</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>58700</v>
+        <v>54400</v>
       </c>
       <c r="E10" s="3">
-        <v>49800</v>
+        <v>58400</v>
       </c>
       <c r="F10" s="3">
-        <v>51300</v>
+        <v>49500</v>
       </c>
       <c r="G10" s="3">
-        <v>49100</v>
+        <v>51000</v>
       </c>
       <c r="H10" s="3">
-        <v>46700</v>
+        <v>48800</v>
       </c>
       <c r="I10" s="3">
-        <v>45400</v>
+        <v>46400</v>
       </c>
       <c r="J10" s="3">
+        <v>45100</v>
+      </c>
+      <c r="K10" s="3">
         <v>30100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>37300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>47700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>34800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>55800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>28100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>30300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>25500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>23100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5200</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V10" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,67 +959,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>8900</v>
+        <v>6900</v>
       </c>
       <c r="E12" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F12" s="3">
         <v>5400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6500</v>
       </c>
-      <c r="H12" s="3">
-        <v>7600</v>
-      </c>
       <c r="I12" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J12" s="3">
         <v>6700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8100</v>
-      </c>
-      <c r="K12" s="3">
-        <v>8600</v>
       </c>
       <c r="L12" s="3">
         <v>8600</v>
       </c>
       <c r="M12" s="3">
+        <v>8600</v>
+      </c>
+      <c r="N12" s="3">
         <v>9000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>19100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>8000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>22000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,28 +1081,31 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3">
-        <v>254700</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>253100</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
@@ -1093,12 +1113,12 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>2300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1114,8 +1134,8 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1123,47 +1143,50 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="3">
-        <v>9300</v>
+      <c r="D15" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F15" s="3">
+        <v>9200</v>
+      </c>
+      <c r="G15" s="3">
         <v>10800</v>
       </c>
-      <c r="G15" s="3">
-        <v>11000</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="H15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="3">
         <v>12300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12100</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3">
         <v>13000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>22100</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>4</v>
+      <c r="D17" s="3">
+        <v>510400</v>
       </c>
       <c r="E17" s="3">
-        <v>456700</v>
+        <v>537500</v>
       </c>
       <c r="F17" s="3">
-        <v>420500</v>
+        <v>453800</v>
       </c>
       <c r="G17" s="3">
-        <v>408600</v>
+        <v>417900</v>
       </c>
       <c r="H17" s="3">
-        <v>723500</v>
+        <v>406100</v>
       </c>
       <c r="I17" s="3">
-        <v>367900</v>
+        <v>719000</v>
       </c>
       <c r="J17" s="3">
+        <v>365600</v>
+      </c>
+      <c r="K17" s="3">
         <v>321700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>323300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>356000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>300300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>568700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>233500</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T17" s="3">
         <v>139500</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-6000</v>
       </c>
       <c r="E18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3900</v>
       </c>
-      <c r="F18" s="3">
-        <v>-8500</v>
-      </c>
       <c r="G18" s="3">
-        <v>-9400</v>
+        <v>-8400</v>
       </c>
       <c r="H18" s="3">
-        <v>-309000</v>
+        <v>-9300</v>
       </c>
       <c r="I18" s="3">
-        <v>-15300</v>
+        <v>-307100</v>
       </c>
       <c r="J18" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-23400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-18600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-21400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-88000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-16000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>-31100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,67 +1376,71 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-4800</v>
       </c>
       <c r="E20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
-        <v>9700</v>
-      </c>
       <c r="J20" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K20" s="3">
         <v>4800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>1300</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1431,215 +1468,227 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
         <v>27200</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3">
         <v>-2900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>-15100</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3">
         <v>200</v>
-      </c>
-      <c r="E22" s="3">
-        <v>300</v>
       </c>
       <c r="F22" s="3">
         <v>300</v>
       </c>
       <c r="G22" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
       </c>
       <c r="I22" s="3">
+        <v>100</v>
+      </c>
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>900</v>
-      </c>
-      <c r="P22" s="3">
-        <v>700</v>
       </c>
       <c r="Q22" s="3">
         <v>700</v>
       </c>
       <c r="R22" s="3">
+        <v>700</v>
+      </c>
+      <c r="S22" s="3">
         <v>1100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3300</v>
       </c>
-      <c r="F23" s="3">
-        <v>-8300</v>
-      </c>
       <c r="G23" s="3">
-        <v>-8500</v>
+        <v>-8200</v>
       </c>
       <c r="H23" s="3">
-        <v>-309000</v>
+        <v>-8400</v>
       </c>
       <c r="I23" s="3">
-        <v>-5900</v>
+        <v>-307000</v>
       </c>
       <c r="J23" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="K23" s="3">
         <v>-18900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-23800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-89600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-17300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-30400</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V23" s="3">
         <v>-40800</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1400</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-1600</v>
       </c>
       <c r="G24" s="3">
         <v>-1600</v>
       </c>
       <c r="H24" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I24" s="3">
         <v>-9900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K24" s="3">
         <v>-1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="M24" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="N24" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="O24" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="P24" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="R24" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="S24" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T24" s="3">
         <v>-1900</v>
       </c>
-      <c r="K24" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="L24" s="3">
-        <v>-11300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="R24" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="V24" s="3">
         <v>-1900</v>
       </c>
-      <c r="T24" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="U24" s="3">
-        <v>-1900</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-10000</v>
       </c>
       <c r="E26" s="3">
+        <v>600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1900</v>
       </c>
-      <c r="F26" s="3">
-        <v>-6700</v>
-      </c>
       <c r="G26" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="H26" s="3">
         <v>-6800</v>
       </c>
-      <c r="H26" s="3">
-        <v>-299000</v>
-      </c>
       <c r="I26" s="3">
+        <v>-297200</v>
+      </c>
+      <c r="J26" s="3">
         <v>-4000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-22000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-84100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13500</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T26" s="3">
         <v>-28500</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-12800</v>
       </c>
       <c r="E27" s="3">
+        <v>400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-6100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-7000</v>
-      </c>
       <c r="H27" s="3">
-        <v>-299100</v>
+        <v>-6900</v>
       </c>
       <c r="I27" s="3">
+        <v>-297200</v>
+      </c>
+      <c r="J27" s="3">
         <v>-4200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-22300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-156300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-86700</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T27" s="3">
         <v>-80200</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,126 +2118,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>4800</v>
       </c>
       <c r="E32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
-        <v>-9700</v>
-      </c>
       <c r="J32" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-4800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1300</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-12800</v>
       </c>
       <c r="E33" s="3">
+        <v>400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-6100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-7000</v>
-      </c>
       <c r="H33" s="3">
-        <v>-299100</v>
+        <v>-6900</v>
       </c>
       <c r="I33" s="3">
+        <v>-297200</v>
+      </c>
+      <c r="J33" s="3">
         <v>-4200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-22300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-156300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-86700</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T33" s="3">
         <v>-80200</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-12800</v>
       </c>
       <c r="E35" s="3">
+        <v>400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-6100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-7000</v>
-      </c>
       <c r="H35" s="3">
-        <v>-299100</v>
+        <v>-6900</v>
       </c>
       <c r="I35" s="3">
+        <v>-297200</v>
+      </c>
+      <c r="J35" s="3">
         <v>-4200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-22300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-156300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-86700</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T35" s="3">
         <v>-80200</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,50 +2483,51 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>275100</v>
+        <v>222400</v>
       </c>
       <c r="E41" s="3">
-        <v>199100</v>
+        <v>273400</v>
       </c>
       <c r="F41" s="3">
-        <v>207500</v>
+        <v>197900</v>
       </c>
       <c r="G41" s="3">
-        <v>217700</v>
+        <v>206300</v>
       </c>
       <c r="H41" s="3">
-        <v>236800</v>
+        <v>216300</v>
       </c>
       <c r="I41" s="3">
-        <v>176600</v>
+        <v>235400</v>
       </c>
       <c r="J41" s="3">
+        <v>175500</v>
+      </c>
+      <c r="K41" s="3">
         <v>169000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>155500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>187300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>269500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>396000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>94400</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2456,49 +2543,52 @@
       <c r="U41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>57100</v>
+        <v>65300</v>
       </c>
       <c r="E42" s="3">
-        <v>48400</v>
+        <v>56700</v>
       </c>
       <c r="F42" s="3">
-        <v>83300</v>
+        <v>48100</v>
       </c>
       <c r="G42" s="3">
-        <v>89600</v>
+        <v>82800</v>
       </c>
       <c r="H42" s="3">
-        <v>108700</v>
+        <v>89000</v>
       </c>
       <c r="I42" s="3">
-        <v>140800</v>
+        <v>108100</v>
       </c>
       <c r="J42" s="3">
+        <v>140000</v>
+      </c>
+      <c r="K42" s="3">
         <v>143300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>121500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>70500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>54000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7100</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>4</v>
@@ -2515,50 +2605,53 @@
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>47600</v>
+        <v>58700</v>
       </c>
       <c r="E43" s="3">
-        <v>77200</v>
+        <v>72600</v>
       </c>
       <c r="F43" s="3">
-        <v>56900</v>
+        <v>76700</v>
       </c>
       <c r="G43" s="3">
-        <v>55000</v>
+        <v>56500</v>
       </c>
       <c r="H43" s="3">
-        <v>94800</v>
+        <v>54600</v>
       </c>
       <c r="I43" s="3">
-        <v>71600</v>
+        <v>94200</v>
       </c>
       <c r="J43" s="3">
+        <v>71100</v>
+      </c>
+      <c r="K43" s="3">
         <v>67600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>99100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>112600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>83400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>70600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>65800</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2574,50 +2667,53 @@
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>141400</v>
+        <v>117100</v>
       </c>
       <c r="E44" s="3">
-        <v>93500</v>
+        <v>140500</v>
       </c>
       <c r="F44" s="3">
-        <v>102200</v>
+        <v>92900</v>
       </c>
       <c r="G44" s="3">
-        <v>81100</v>
+        <v>101600</v>
       </c>
       <c r="H44" s="3">
-        <v>60300</v>
+        <v>80600</v>
       </c>
       <c r="I44" s="3">
-        <v>63100</v>
+        <v>59900</v>
       </c>
       <c r="J44" s="3">
+        <v>62700</v>
+      </c>
+      <c r="K44" s="3">
         <v>93600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>92200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>66100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>71100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>50100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>45600</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2633,50 +2729,53 @@
       <c r="U44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>108100</v>
+        <v>119600</v>
       </c>
       <c r="E45" s="3">
-        <v>113100</v>
+        <v>82200</v>
       </c>
       <c r="F45" s="3">
-        <v>94300</v>
+        <v>112400</v>
       </c>
       <c r="G45" s="3">
-        <v>84500</v>
+        <v>93700</v>
       </c>
       <c r="H45" s="3">
-        <v>40200</v>
+        <v>84000</v>
       </c>
       <c r="I45" s="3">
-        <v>96000</v>
+        <v>39900</v>
       </c>
       <c r="J45" s="3">
+        <v>95400</v>
+      </c>
+      <c r="K45" s="3">
         <v>96900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>107300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>136700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>117000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>79900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>63100</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2692,50 +2791,53 @@
       <c r="U45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>629300</v>
+        <v>583200</v>
       </c>
       <c r="E46" s="3">
-        <v>531300</v>
+        <v>625400</v>
       </c>
       <c r="F46" s="3">
-        <v>544200</v>
+        <v>528000</v>
       </c>
       <c r="G46" s="3">
-        <v>527800</v>
+        <v>540800</v>
       </c>
       <c r="H46" s="3">
-        <v>540800</v>
+        <v>524600</v>
       </c>
       <c r="I46" s="3">
-        <v>548100</v>
+        <v>537500</v>
       </c>
       <c r="J46" s="3">
+        <v>544700</v>
+      </c>
+      <c r="K46" s="3">
         <v>570500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>575700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>573100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>595100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>603700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>268800</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2751,50 +2853,53 @@
       <c r="U46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>64900</v>
+        <v>66600</v>
       </c>
       <c r="E47" s="3">
-        <v>65200</v>
+        <v>64500</v>
       </c>
       <c r="F47" s="3">
-        <v>67500</v>
+        <v>64800</v>
       </c>
       <c r="G47" s="3">
-        <v>68600</v>
+        <v>67100</v>
       </c>
       <c r="H47" s="3">
-        <v>30500</v>
+        <v>68200</v>
       </c>
       <c r="I47" s="3">
-        <v>31900</v>
+        <v>30300</v>
       </c>
       <c r="J47" s="3">
+        <v>31700</v>
+      </c>
+      <c r="K47" s="3">
         <v>32600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>32800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>33400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>29200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>16200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>15100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2810,50 +2915,53 @@
       <c r="U47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>20600</v>
+        <v>20700</v>
       </c>
       <c r="E48" s="3">
-        <v>18200</v>
+        <v>20500</v>
       </c>
       <c r="F48" s="3">
-        <v>16800</v>
+        <v>18100</v>
       </c>
       <c r="G48" s="3">
+        <v>16700</v>
+      </c>
+      <c r="H48" s="3">
         <v>15500</v>
       </c>
-      <c r="H48" s="3">
-        <v>16500</v>
-      </c>
       <c r="I48" s="3">
-        <v>16500</v>
+        <v>16400</v>
       </c>
       <c r="J48" s="3">
+        <v>16300</v>
+      </c>
+      <c r="K48" s="3">
         <v>16100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2869,50 +2977,53 @@
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>37600</v>
+        <v>28100</v>
       </c>
       <c r="E49" s="3">
-        <v>46900</v>
+        <v>37400</v>
       </c>
       <c r="F49" s="3">
-        <v>56200</v>
+        <v>46600</v>
       </c>
       <c r="G49" s="3">
-        <v>66000</v>
+        <v>55900</v>
       </c>
       <c r="H49" s="3">
-        <v>75700</v>
+        <v>65600</v>
       </c>
       <c r="I49" s="3">
-        <v>368800</v>
+        <v>75200</v>
       </c>
       <c r="J49" s="3">
+        <v>366500</v>
+      </c>
+      <c r="K49" s="3">
         <v>380000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>386400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>397600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>421200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>432800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>444300</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2928,8 +3039,11 @@
       <c r="U49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,50 +3163,53 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>11200</v>
+        <v>15800</v>
       </c>
       <c r="E52" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F52" s="3">
         <v>10700</v>
       </c>
-      <c r="F52" s="3">
-        <v>11500</v>
-      </c>
       <c r="G52" s="3">
-        <v>12200</v>
+        <v>11400</v>
       </c>
       <c r="H52" s="3">
-        <v>38300</v>
+        <v>12100</v>
       </c>
       <c r="I52" s="3">
-        <v>14400</v>
+        <v>38100</v>
       </c>
       <c r="J52" s="3">
+        <v>14300</v>
+      </c>
+      <c r="K52" s="3">
         <v>12700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>20500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2400</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,50 +3287,53 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>763600</v>
+        <v>714500</v>
       </c>
       <c r="E54" s="3">
-        <v>672400</v>
+        <v>758900</v>
       </c>
       <c r="F54" s="3">
-        <v>696200</v>
+        <v>668200</v>
       </c>
       <c r="G54" s="3">
-        <v>690100</v>
+        <v>691900</v>
       </c>
       <c r="H54" s="3">
-        <v>701900</v>
+        <v>685900</v>
       </c>
       <c r="I54" s="3">
-        <v>979600</v>
+        <v>697500</v>
       </c>
       <c r="J54" s="3">
+        <v>973600</v>
+      </c>
+      <c r="K54" s="3">
         <v>1011900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1023500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1036000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1078300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1077800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>739900</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3223,8 +3349,11 @@
       <c r="U54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,50 +3399,51 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>74000</v>
+        <v>18500</v>
       </c>
       <c r="E57" s="3">
-        <v>16200</v>
+        <v>73500</v>
       </c>
       <c r="F57" s="3">
-        <v>9800</v>
+        <v>16100</v>
       </c>
       <c r="G57" s="3">
-        <v>11800</v>
+        <v>9700</v>
       </c>
       <c r="H57" s="3">
-        <v>10200</v>
+        <v>11700</v>
       </c>
       <c r="I57" s="3">
-        <v>7900</v>
+        <v>10100</v>
       </c>
       <c r="J57" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K57" s="3">
         <v>9300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3328,50 +3459,53 @@
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>48600</v>
+        <v>77400</v>
       </c>
       <c r="E58" s="3">
-        <v>27800</v>
+        <v>48300</v>
       </c>
       <c r="F58" s="3">
-        <v>38800</v>
+        <v>27600</v>
       </c>
       <c r="G58" s="3">
-        <v>44300</v>
+        <v>38500</v>
       </c>
       <c r="H58" s="3">
-        <v>17200</v>
+        <v>44100</v>
       </c>
       <c r="I58" s="3">
+        <v>17100</v>
+      </c>
+      <c r="J58" s="3">
         <v>10500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>29700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>63500</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3387,50 +3521,53 @@
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>112500</v>
+        <v>100300</v>
       </c>
       <c r="E59" s="3">
-        <v>94600</v>
+        <v>111800</v>
       </c>
       <c r="F59" s="3">
-        <v>107200</v>
+        <v>94000</v>
       </c>
       <c r="G59" s="3">
-        <v>85000</v>
+        <v>106600</v>
       </c>
       <c r="H59" s="3">
-        <v>114700</v>
+        <v>84500</v>
       </c>
       <c r="I59" s="3">
-        <v>100100</v>
+        <v>114000</v>
       </c>
       <c r="J59" s="3">
+        <v>99500</v>
+      </c>
+      <c r="K59" s="3">
         <v>114800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>106100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>95000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>83000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>77700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>85300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3446,50 +3583,53 @@
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>235100</v>
+        <v>196200</v>
       </c>
       <c r="E60" s="3">
-        <v>138600</v>
+        <v>233700</v>
       </c>
       <c r="F60" s="3">
-        <v>155800</v>
+        <v>137800</v>
       </c>
       <c r="G60" s="3">
-        <v>141100</v>
+        <v>154800</v>
       </c>
       <c r="H60" s="3">
-        <v>142100</v>
+        <v>140200</v>
       </c>
       <c r="I60" s="3">
-        <v>118500</v>
+        <v>141200</v>
       </c>
       <c r="J60" s="3">
+        <v>117800</v>
+      </c>
+      <c r="K60" s="3">
         <v>144400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>137800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>113900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>110100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>114300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>155100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3505,8 +3645,11 @@
       <c r="U60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3538,17 +3681,17 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3564,50 +3707,53 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E62" s="3">
         <v>12500</v>
       </c>
-      <c r="E62" s="3">
-        <v>13600</v>
-      </c>
       <c r="F62" s="3">
-        <v>14700</v>
+        <v>13500</v>
       </c>
       <c r="G62" s="3">
-        <v>17100</v>
+        <v>14600</v>
       </c>
       <c r="H62" s="3">
-        <v>20100</v>
+        <v>17000</v>
       </c>
       <c r="I62" s="3">
-        <v>30800</v>
+        <v>20000</v>
       </c>
       <c r="J62" s="3">
+        <v>30600</v>
+      </c>
+      <c r="K62" s="3">
         <v>32400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>33900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>35600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>46600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>52600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>46300</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3623,8 +3769,11 @@
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,50 +3955,53 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>247700</v>
+        <v>206600</v>
       </c>
       <c r="E66" s="3">
-        <v>152200</v>
+        <v>246100</v>
       </c>
       <c r="F66" s="3">
-        <v>170500</v>
+        <v>151200</v>
       </c>
       <c r="G66" s="3">
-        <v>158200</v>
+        <v>169400</v>
       </c>
       <c r="H66" s="3">
-        <v>162200</v>
+        <v>157200</v>
       </c>
       <c r="I66" s="3">
-        <v>149300</v>
+        <v>161200</v>
       </c>
       <c r="J66" s="3">
+        <v>148400</v>
+      </c>
+      <c r="K66" s="3">
         <v>176800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>171700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>149400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>157500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>168900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>204600</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3859,8 +4017,11 @@
       <c r="U66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4039,11 +4207,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>1370500</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,16 +4289,19 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>4</v>
+      <c r="E72" s="3">
+        <v>-1266000</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>4</v>
@@ -4135,11 +4309,11 @@
       <c r="G72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H72" s="3">
-        <v>-1252100</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-1244400</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
@@ -4147,21 +4321,21 @@
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-902900</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>-835500</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4177,8 +4351,11 @@
       <c r="U72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,50 +4537,53 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>516000</v>
+        <v>507800</v>
       </c>
       <c r="E76" s="3">
-        <v>520200</v>
+        <v>512800</v>
       </c>
       <c r="F76" s="3">
-        <v>525700</v>
+        <v>517000</v>
       </c>
       <c r="G76" s="3">
-        <v>531900</v>
+        <v>522500</v>
       </c>
       <c r="H76" s="3">
-        <v>539600</v>
+        <v>528600</v>
       </c>
       <c r="I76" s="3">
-        <v>830300</v>
+        <v>536300</v>
       </c>
       <c r="J76" s="3">
+        <v>825200</v>
+      </c>
+      <c r="K76" s="3">
         <v>835000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>851800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>886500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>920700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>908900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-835200</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4413,8 +4599,11 @@
       <c r="U76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-12800</v>
       </c>
       <c r="E81" s="3">
+        <v>400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-6100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-7000</v>
-      </c>
       <c r="H81" s="3">
-        <v>-299100</v>
+        <v>-6900</v>
       </c>
       <c r="I81" s="3">
+        <v>-297200</v>
+      </c>
+      <c r="J81" s="3">
         <v>-4200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-22300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-156300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-86700</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T81" s="3">
         <v>-80200</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,8 +4816,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4656,8 +4855,8 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>4</v>
@@ -4677,8 +4876,11 @@
       <c r="U83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,8 +5186,11 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5010,8 +5227,8 @@
       <c r="N89" s="3">
         <v>0</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
+      <c r="O89" s="3">
+        <v>0</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>4</v>
@@ -5031,8 +5248,11 @@
       <c r="U89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,8 +5274,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5092,8 +5313,8 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>4</v>
@@ -5113,8 +5334,11 @@
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,8 +5458,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5269,8 +5499,8 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>4</v>
@@ -5290,8 +5520,11 @@
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,8 +5792,11 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5587,8 +5833,8 @@
       <c r="N100" s="3">
         <v>0</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>4</v>
@@ -5608,8 +5854,11 @@
       <c r="U100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5646,8 +5895,8 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>4</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>4</v>
@@ -5667,8 +5916,11 @@
       <c r="U101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5705,8 +5957,8 @@
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>4</v>
@@ -5724,6 +5976,9 @@
         <v>4</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
   <si>
     <t>RERE</t>
   </si>
@@ -656,288 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>504400</v>
+        <v>532400</v>
       </c>
       <c r="E8" s="3">
-        <v>535200</v>
+        <v>514700</v>
       </c>
       <c r="F8" s="3">
-        <v>450000</v>
+        <v>546100</v>
       </c>
       <c r="G8" s="3">
-        <v>409500</v>
+        <v>459100</v>
       </c>
       <c r="H8" s="3">
-        <v>396800</v>
+        <v>417800</v>
       </c>
       <c r="I8" s="3">
-        <v>411900</v>
+        <v>404900</v>
       </c>
       <c r="J8" s="3">
+        <v>420300</v>
+      </c>
+      <c r="K8" s="3">
         <v>350400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>298300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>304700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>336300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>278900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>480800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>217500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>228900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>195400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>176200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>108400</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V8" s="3">
+      <c r="V8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W8" s="3">
         <v>152300</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>450100</v>
+        <v>467900</v>
       </c>
       <c r="E9" s="3">
-        <v>476800</v>
+        <v>459300</v>
       </c>
       <c r="F9" s="3">
-        <v>400500</v>
+        <v>486500</v>
       </c>
       <c r="G9" s="3">
-        <v>358500</v>
+        <v>408700</v>
       </c>
       <c r="H9" s="3">
-        <v>348000</v>
+        <v>365800</v>
       </c>
       <c r="I9" s="3">
-        <v>365500</v>
+        <v>355100</v>
       </c>
       <c r="J9" s="3">
+        <v>373000</v>
+      </c>
+      <c r="K9" s="3">
         <v>305200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>268200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>267400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>288700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>244100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>425000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>189400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>198600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>169900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>153100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>103100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>590400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>149000</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>54400</v>
+        <v>64500</v>
       </c>
       <c r="E10" s="3">
-        <v>58400</v>
+        <v>55500</v>
       </c>
       <c r="F10" s="3">
-        <v>49500</v>
+        <v>59600</v>
       </c>
       <c r="G10" s="3">
-        <v>51000</v>
+        <v>50500</v>
       </c>
       <c r="H10" s="3">
-        <v>48800</v>
+        <v>52000</v>
       </c>
       <c r="I10" s="3">
-        <v>46400</v>
+        <v>49800</v>
       </c>
       <c r="J10" s="3">
+        <v>47300</v>
+      </c>
+      <c r="K10" s="3">
         <v>45100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>30100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>37300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>47700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>34800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>55800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>28100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>30300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>25500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>23100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5200</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W10" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="E12" s="3">
-        <v>8800</v>
+        <v>7000</v>
       </c>
       <c r="F12" s="3">
-        <v>5400</v>
+        <v>9000</v>
       </c>
       <c r="G12" s="3">
-        <v>6200</v>
+        <v>5500</v>
       </c>
       <c r="H12" s="3">
-        <v>6500</v>
+        <v>6300</v>
       </c>
       <c r="I12" s="3">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="J12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="K12" s="3">
         <v>6700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8100</v>
-      </c>
-      <c r="L12" s="3">
-        <v>8600</v>
       </c>
       <c r="M12" s="3">
         <v>8600</v>
       </c>
       <c r="N12" s="3">
+        <v>8600</v>
+      </c>
+      <c r="O12" s="3">
         <v>9000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>19100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>22000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,31 +1101,34 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
-        <v>253100</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>258300</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
@@ -1116,12 +1136,12 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>2300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1137,8 +1157,8 @@
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1146,50 +1166,53 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>9200</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="3">
-        <v>9200</v>
+        <v>8000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G15" s="3">
-        <v>10800</v>
+        <v>9400</v>
       </c>
       <c r="H15" s="3">
-        <v>10900</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="3">
+        <v>11000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>11100</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K15" s="3">
         <v>12300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12100</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3">
         <v>13000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>22100</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>510400</v>
+        <v>533200</v>
       </c>
       <c r="E17" s="3">
-        <v>537500</v>
+        <v>520900</v>
       </c>
       <c r="F17" s="3">
-        <v>453800</v>
+        <v>548500</v>
       </c>
       <c r="G17" s="3">
-        <v>417900</v>
+        <v>463100</v>
       </c>
       <c r="H17" s="3">
-        <v>406100</v>
+        <v>426400</v>
       </c>
       <c r="I17" s="3">
-        <v>719000</v>
+        <v>414400</v>
       </c>
       <c r="J17" s="3">
+        <v>733700</v>
+      </c>
+      <c r="K17" s="3">
         <v>365600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>321700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>323300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>356000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>300300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>568700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>233500</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U17" s="3">
         <v>139500</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-6000</v>
+        <v>-800</v>
       </c>
       <c r="E18" s="3">
-        <v>-2300</v>
+        <v>-6100</v>
       </c>
       <c r="F18" s="3">
-        <v>-3900</v>
+        <v>-2400</v>
       </c>
       <c r="G18" s="3">
-        <v>-8400</v>
+        <v>-4000</v>
       </c>
       <c r="H18" s="3">
-        <v>-9300</v>
+        <v>-8600</v>
       </c>
       <c r="I18" s="3">
-        <v>-307100</v>
+        <v>-9500</v>
       </c>
       <c r="J18" s="3">
+        <v>-313400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-15200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-23400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-18600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-19700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-21400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-88000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3">
         <v>-31100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,70 +1410,74 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>900</v>
+      </c>
+      <c r="H20" s="3">
+        <v>500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3">
+        <v>9600</v>
+      </c>
+      <c r="L20" s="3">
+        <v>4800</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="N20" s="3">
         <v>-4800</v>
       </c>
-      <c r="E20" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>900</v>
-      </c>
-      <c r="G20" s="3">
-        <v>500</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>9600</v>
-      </c>
-      <c r="K20" s="3">
-        <v>4800</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3">
         <v>1300</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1471,55 +1508,58 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>27200</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
         <v>-15100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E22" s="3">
+        <v>600</v>
+      </c>
+      <c r="F22" s="3">
         <v>200</v>
-      </c>
-      <c r="F22" s="3">
-        <v>300</v>
       </c>
       <c r="G22" s="3">
         <v>300</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
@@ -1528,167 +1568,176 @@
         <v>200</v>
       </c>
       <c r="K22" s="3">
+        <v>200</v>
+      </c>
+      <c r="L22" s="3">
         <v>300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>900</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>700</v>
       </c>
       <c r="R22" s="3">
         <v>700</v>
       </c>
       <c r="S22" s="3">
+        <v>700</v>
+      </c>
+      <c r="T22" s="3">
         <v>1100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-11400</v>
+        <v>-700</v>
       </c>
       <c r="E23" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3300</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-8200</v>
       </c>
       <c r="H23" s="3">
         <v>-8400</v>
       </c>
       <c r="I23" s="3">
-        <v>-307000</v>
+        <v>-8600</v>
       </c>
       <c r="J23" s="3">
+        <v>-313300</v>
+      </c>
+      <c r="K23" s="3">
         <v>-5800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-18900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-23800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-89600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-15400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-17300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-30400</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W23" s="3">
         <v>-40800</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1400</v>
       </c>
-      <c r="E24" s="3">
-        <v>-1200</v>
-      </c>
       <c r="F24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="G24" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-1600</v>
       </c>
       <c r="H24" s="3">
         <v>-1600</v>
       </c>
       <c r="I24" s="3">
-        <v>-9900</v>
+        <v>-1700</v>
       </c>
       <c r="J24" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="K24" s="3">
         <v>-1800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-11300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-5500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-4600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-10000</v>
+        <v>500</v>
       </c>
       <c r="E26" s="3">
-        <v>600</v>
+        <v>-10200</v>
       </c>
       <c r="F26" s="3">
+        <v>700</v>
+      </c>
+      <c r="G26" s="3">
         <v>-1900</v>
       </c>
-      <c r="G26" s="3">
-        <v>-6600</v>
-      </c>
       <c r="H26" s="3">
-        <v>-6800</v>
+        <v>-6700</v>
       </c>
       <c r="I26" s="3">
-        <v>-297200</v>
+        <v>-6900</v>
       </c>
       <c r="J26" s="3">
+        <v>-303200</v>
+      </c>
+      <c r="K26" s="3">
         <v>-4000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-17000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-22000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-17300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-84100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U26" s="3">
         <v>-28500</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-12800</v>
+        <v>-1500</v>
       </c>
       <c r="E27" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="F27" s="3">
         <v>400</v>
       </c>
-      <c r="F27" s="3">
-        <v>-6100</v>
-      </c>
       <c r="G27" s="3">
-        <v>-9000</v>
+        <v>-6200</v>
       </c>
       <c r="H27" s="3">
-        <v>-6900</v>
+        <v>-9100</v>
       </c>
       <c r="I27" s="3">
-        <v>-297200</v>
+        <v>-7000</v>
       </c>
       <c r="J27" s="3">
+        <v>-303300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-4200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-22300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-17300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-156300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-86700</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U27" s="3">
         <v>-80200</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="M32" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N32" s="3">
         <v>4800</v>
       </c>
-      <c r="E32" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="L32" s="3">
-        <v>5100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>4800</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3">
         <v>-1300</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-12800</v>
+        <v>-1500</v>
       </c>
       <c r="E33" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="F33" s="3">
         <v>400</v>
       </c>
-      <c r="F33" s="3">
-        <v>-6100</v>
-      </c>
       <c r="G33" s="3">
-        <v>-9000</v>
+        <v>-6200</v>
       </c>
       <c r="H33" s="3">
-        <v>-6900</v>
+        <v>-9100</v>
       </c>
       <c r="I33" s="3">
-        <v>-297200</v>
+        <v>-7000</v>
       </c>
       <c r="J33" s="3">
+        <v>-303300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-4200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-22300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-17300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-156300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-86700</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U33" s="3">
         <v>-80200</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-12800</v>
+        <v>-1500</v>
       </c>
       <c r="E35" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="F35" s="3">
         <v>400</v>
       </c>
-      <c r="F35" s="3">
-        <v>-6100</v>
-      </c>
       <c r="G35" s="3">
-        <v>-9000</v>
+        <v>-6200</v>
       </c>
       <c r="H35" s="3">
-        <v>-6900</v>
+        <v>-9100</v>
       </c>
       <c r="I35" s="3">
-        <v>-297200</v>
+        <v>-7000</v>
       </c>
       <c r="J35" s="3">
+        <v>-303300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-4200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-22300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-17300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-156300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-86700</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U35" s="3">
         <v>-80200</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,53 +2570,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>222400</v>
+        <v>231600</v>
       </c>
       <c r="E41" s="3">
-        <v>273400</v>
+        <v>227000</v>
       </c>
       <c r="F41" s="3">
-        <v>197900</v>
+        <v>279000</v>
       </c>
       <c r="G41" s="3">
-        <v>206300</v>
+        <v>201900</v>
       </c>
       <c r="H41" s="3">
-        <v>216300</v>
+        <v>210500</v>
       </c>
       <c r="I41" s="3">
-        <v>235400</v>
+        <v>220700</v>
       </c>
       <c r="J41" s="3">
+        <v>240200</v>
+      </c>
+      <c r="K41" s="3">
         <v>175500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>169000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>155500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>187300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>269500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>396000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>94400</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2546,52 +2633,55 @@
       <c r="V41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>65300</v>
+        <v>89900</v>
       </c>
       <c r="E42" s="3">
-        <v>56700</v>
+        <v>66600</v>
       </c>
       <c r="F42" s="3">
-        <v>48100</v>
+        <v>57900</v>
       </c>
       <c r="G42" s="3">
-        <v>82800</v>
+        <v>49100</v>
       </c>
       <c r="H42" s="3">
-        <v>89000</v>
+        <v>84400</v>
       </c>
       <c r="I42" s="3">
-        <v>108100</v>
+        <v>90800</v>
       </c>
       <c r="J42" s="3">
+        <v>110300</v>
+      </c>
+      <c r="K42" s="3">
         <v>140000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>143300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>121500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>70500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>54000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>7100</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>4</v>
@@ -2608,53 +2698,56 @@
       <c r="V42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>58700</v>
+        <v>61400</v>
       </c>
       <c r="E43" s="3">
-        <v>72600</v>
+        <v>59900</v>
       </c>
       <c r="F43" s="3">
-        <v>76700</v>
+        <v>74000</v>
       </c>
       <c r="G43" s="3">
-        <v>56500</v>
+        <v>78300</v>
       </c>
       <c r="H43" s="3">
-        <v>54600</v>
+        <v>57700</v>
       </c>
       <c r="I43" s="3">
-        <v>94200</v>
+        <v>55700</v>
       </c>
       <c r="J43" s="3">
+        <v>96100</v>
+      </c>
+      <c r="K43" s="3">
         <v>71100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>67600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>99100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>112600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>83400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>70600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>65800</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2670,53 +2763,56 @@
       <c r="V43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>117100</v>
+        <v>93100</v>
       </c>
       <c r="E44" s="3">
-        <v>140500</v>
+        <v>119500</v>
       </c>
       <c r="F44" s="3">
-        <v>92900</v>
+        <v>143400</v>
       </c>
       <c r="G44" s="3">
-        <v>101600</v>
+        <v>94800</v>
       </c>
       <c r="H44" s="3">
-        <v>80600</v>
+        <v>103700</v>
       </c>
       <c r="I44" s="3">
-        <v>59900</v>
+        <v>82200</v>
       </c>
       <c r="J44" s="3">
+        <v>61100</v>
+      </c>
+      <c r="K44" s="3">
         <v>62700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>93600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>92200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>66100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>71100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>50100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>45600</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2732,53 +2828,56 @@
       <c r="V44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>119600</v>
+        <v>117400</v>
       </c>
       <c r="E45" s="3">
-        <v>82200</v>
+        <v>122100</v>
       </c>
       <c r="F45" s="3">
-        <v>112400</v>
+        <v>83900</v>
       </c>
       <c r="G45" s="3">
-        <v>93700</v>
+        <v>114700</v>
       </c>
       <c r="H45" s="3">
-        <v>84000</v>
+        <v>95600</v>
       </c>
       <c r="I45" s="3">
-        <v>39900</v>
+        <v>85700</v>
       </c>
       <c r="J45" s="3">
+        <v>40700</v>
+      </c>
+      <c r="K45" s="3">
         <v>95400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>96900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>107300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>136700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>117000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>79900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>63100</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2794,53 +2893,56 @@
       <c r="V45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>583200</v>
+        <v>593400</v>
       </c>
       <c r="E46" s="3">
-        <v>625400</v>
+        <v>595100</v>
       </c>
       <c r="F46" s="3">
-        <v>528000</v>
+        <v>638200</v>
       </c>
       <c r="G46" s="3">
-        <v>540800</v>
+        <v>538800</v>
       </c>
       <c r="H46" s="3">
-        <v>524600</v>
+        <v>551900</v>
       </c>
       <c r="I46" s="3">
-        <v>537500</v>
+        <v>535300</v>
       </c>
       <c r="J46" s="3">
+        <v>548400</v>
+      </c>
+      <c r="K46" s="3">
         <v>544700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>570500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>575700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>573100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>595100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>603700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>268800</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2856,53 +2958,56 @@
       <c r="V46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>66600</v>
+        <v>78200</v>
       </c>
       <c r="E47" s="3">
-        <v>64500</v>
+        <v>68000</v>
       </c>
       <c r="F47" s="3">
-        <v>64800</v>
+        <v>65900</v>
       </c>
       <c r="G47" s="3">
-        <v>67100</v>
+        <v>66200</v>
       </c>
       <c r="H47" s="3">
-        <v>68200</v>
+        <v>68400</v>
       </c>
       <c r="I47" s="3">
-        <v>30300</v>
+        <v>69600</v>
       </c>
       <c r="J47" s="3">
+        <v>31000</v>
+      </c>
+      <c r="K47" s="3">
         <v>31700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>32600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>32800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>33400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>29200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>16200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>15100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2918,53 +3023,56 @@
       <c r="V47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>20700</v>
+        <v>20500</v>
       </c>
       <c r="E48" s="3">
-        <v>20500</v>
+        <v>21200</v>
       </c>
       <c r="F48" s="3">
-        <v>18100</v>
+        <v>20900</v>
       </c>
       <c r="G48" s="3">
+        <v>18500</v>
+      </c>
+      <c r="H48" s="3">
+        <v>17100</v>
+      </c>
+      <c r="I48" s="3">
+        <v>15800</v>
+      </c>
+      <c r="J48" s="3">
         <v>16700</v>
       </c>
-      <c r="H48" s="3">
-        <v>15500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>16400</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>16300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9300</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2980,53 +3088,56 @@
       <c r="V48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>28100</v>
+        <v>20700</v>
       </c>
       <c r="E49" s="3">
-        <v>37400</v>
+        <v>28700</v>
       </c>
       <c r="F49" s="3">
-        <v>46600</v>
+        <v>38200</v>
       </c>
       <c r="G49" s="3">
-        <v>55900</v>
+        <v>47600</v>
       </c>
       <c r="H49" s="3">
-        <v>65600</v>
+        <v>57000</v>
       </c>
       <c r="I49" s="3">
-        <v>75200</v>
+        <v>66900</v>
       </c>
       <c r="J49" s="3">
+        <v>76800</v>
+      </c>
+      <c r="K49" s="3">
         <v>366500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>380000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>386400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>397600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>421200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>432800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>444300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,53 +3283,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>15800</v>
+        <v>9500</v>
       </c>
       <c r="E52" s="3">
-        <v>11100</v>
+        <v>16100</v>
       </c>
       <c r="F52" s="3">
-        <v>10700</v>
+        <v>11300</v>
       </c>
       <c r="G52" s="3">
-        <v>11400</v>
+        <v>10900</v>
       </c>
       <c r="H52" s="3">
-        <v>12100</v>
+        <v>11600</v>
       </c>
       <c r="I52" s="3">
-        <v>38100</v>
+        <v>12400</v>
       </c>
       <c r="J52" s="3">
+        <v>38900</v>
+      </c>
+      <c r="K52" s="3">
         <v>14300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>20500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2400</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,53 +3413,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>714500</v>
+        <v>722200</v>
       </c>
       <c r="E54" s="3">
-        <v>758900</v>
+        <v>729100</v>
       </c>
       <c r="F54" s="3">
-        <v>668200</v>
+        <v>774400</v>
       </c>
       <c r="G54" s="3">
-        <v>691900</v>
+        <v>681900</v>
       </c>
       <c r="H54" s="3">
-        <v>685900</v>
+        <v>706000</v>
       </c>
       <c r="I54" s="3">
-        <v>697500</v>
+        <v>699900</v>
       </c>
       <c r="J54" s="3">
+        <v>711800</v>
+      </c>
+      <c r="K54" s="3">
         <v>973600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1011900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1023500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1036000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1078300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1077800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>739900</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3352,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,53 +3530,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>18500</v>
+        <v>10300</v>
       </c>
       <c r="E57" s="3">
-        <v>73500</v>
+        <v>18900</v>
       </c>
       <c r="F57" s="3">
-        <v>16100</v>
+        <v>75000</v>
       </c>
       <c r="G57" s="3">
-        <v>9700</v>
+        <v>16400</v>
       </c>
       <c r="H57" s="3">
-        <v>11700</v>
+        <v>9900</v>
       </c>
       <c r="I57" s="3">
-        <v>10100</v>
+        <v>11900</v>
       </c>
       <c r="J57" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K57" s="3">
         <v>7800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3462,53 +3593,56 @@
       <c r="V57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>77400</v>
+        <v>65600</v>
       </c>
       <c r="E58" s="3">
-        <v>48300</v>
+        <v>79000</v>
       </c>
       <c r="F58" s="3">
-        <v>27600</v>
+        <v>49300</v>
       </c>
       <c r="G58" s="3">
-        <v>38500</v>
+        <v>28200</v>
       </c>
       <c r="H58" s="3">
-        <v>44100</v>
+        <v>39300</v>
       </c>
       <c r="I58" s="3">
-        <v>17100</v>
+        <v>45000</v>
       </c>
       <c r="J58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="K58" s="3">
         <v>10500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>20300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>21300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>20200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>29700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>63500</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3524,53 +3658,56 @@
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100300</v>
+        <v>122700</v>
       </c>
       <c r="E59" s="3">
-        <v>111800</v>
+        <v>102400</v>
       </c>
       <c r="F59" s="3">
-        <v>94000</v>
+        <v>114100</v>
       </c>
       <c r="G59" s="3">
-        <v>106600</v>
+        <v>95900</v>
       </c>
       <c r="H59" s="3">
-        <v>84500</v>
+        <v>108800</v>
       </c>
       <c r="I59" s="3">
-        <v>114000</v>
+        <v>86200</v>
       </c>
       <c r="J59" s="3">
+        <v>116300</v>
+      </c>
+      <c r="K59" s="3">
         <v>99500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>114800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>106100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>95000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>83000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>77700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>85300</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3586,53 +3723,56 @@
       <c r="V59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>196200</v>
+        <v>198600</v>
       </c>
       <c r="E60" s="3">
-        <v>233700</v>
+        <v>200200</v>
       </c>
       <c r="F60" s="3">
+        <v>238500</v>
+      </c>
+      <c r="G60" s="3">
+        <v>140600</v>
+      </c>
+      <c r="H60" s="3">
+        <v>158000</v>
+      </c>
+      <c r="I60" s="3">
+        <v>143100</v>
+      </c>
+      <c r="J60" s="3">
+        <v>144100</v>
+      </c>
+      <c r="K60" s="3">
+        <v>117800</v>
+      </c>
+      <c r="L60" s="3">
+        <v>144400</v>
+      </c>
+      <c r="M60" s="3">
         <v>137800</v>
       </c>
-      <c r="G60" s="3">
-        <v>154800</v>
-      </c>
-      <c r="H60" s="3">
-        <v>140200</v>
-      </c>
-      <c r="I60" s="3">
-        <v>141200</v>
-      </c>
-      <c r="J60" s="3">
-        <v>117800</v>
-      </c>
-      <c r="K60" s="3">
-        <v>144400</v>
-      </c>
-      <c r="L60" s="3">
-        <v>137800</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>113900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>110100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>114300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>155100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3648,8 +3788,11 @@
       <c r="V60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3684,17 +3827,17 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3200</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3710,53 +3853,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10400</v>
+        <v>9000</v>
       </c>
       <c r="E62" s="3">
-        <v>12500</v>
+        <v>10600</v>
       </c>
       <c r="F62" s="3">
-        <v>13500</v>
+        <v>12700</v>
       </c>
       <c r="G62" s="3">
-        <v>14600</v>
+        <v>13800</v>
       </c>
       <c r="H62" s="3">
-        <v>17000</v>
+        <v>14900</v>
       </c>
       <c r="I62" s="3">
-        <v>20000</v>
+        <v>17400</v>
       </c>
       <c r="J62" s="3">
+        <v>20400</v>
+      </c>
+      <c r="K62" s="3">
         <v>30600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>32400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>33900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>35600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>46600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>52600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>46300</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,53 +4113,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>206600</v>
+        <v>207600</v>
       </c>
       <c r="E66" s="3">
-        <v>246100</v>
+        <v>210900</v>
       </c>
       <c r="F66" s="3">
-        <v>151200</v>
+        <v>251200</v>
       </c>
       <c r="G66" s="3">
-        <v>169400</v>
+        <v>154300</v>
       </c>
       <c r="H66" s="3">
-        <v>157200</v>
+        <v>172900</v>
       </c>
       <c r="I66" s="3">
-        <v>161200</v>
+        <v>160500</v>
       </c>
       <c r="J66" s="3">
+        <v>164500</v>
+      </c>
+      <c r="K66" s="3">
         <v>148400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>176800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>171700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>149400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>157500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>168900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>204600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4020,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4210,11 +4378,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>1370500</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,19 +4463,22 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E72" s="3">
-        <v>-1266000</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-1291800</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>4</v>
@@ -4312,11 +4486,11 @@
       <c r="H72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I72" s="3">
-        <v>-1244400</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-1269800</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
@@ -4324,21 +4498,21 @@
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-902900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-835500</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4354,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,53 +4723,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>507800</v>
+        <v>514600</v>
       </c>
       <c r="E76" s="3">
-        <v>512800</v>
+        <v>518200</v>
       </c>
       <c r="F76" s="3">
-        <v>517000</v>
+        <v>523200</v>
       </c>
       <c r="G76" s="3">
-        <v>522500</v>
+        <v>527600</v>
       </c>
       <c r="H76" s="3">
-        <v>528600</v>
+        <v>533100</v>
       </c>
       <c r="I76" s="3">
-        <v>536300</v>
+        <v>539400</v>
       </c>
       <c r="J76" s="3">
+        <v>547200</v>
+      </c>
+      <c r="K76" s="3">
         <v>825200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>835000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>851800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>886500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>920700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>908900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-835200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4602,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-12800</v>
+        <v>-1500</v>
       </c>
       <c r="E81" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="F81" s="3">
         <v>400</v>
       </c>
-      <c r="F81" s="3">
-        <v>-6100</v>
-      </c>
       <c r="G81" s="3">
-        <v>-9000</v>
+        <v>-6200</v>
       </c>
       <c r="H81" s="3">
-        <v>-6900</v>
+        <v>-9100</v>
       </c>
       <c r="I81" s="3">
-        <v>-297200</v>
+        <v>-7000</v>
       </c>
       <c r="J81" s="3">
+        <v>-303300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-4200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-22300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-17300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-156300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-86700</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U81" s="3">
         <v>-80200</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,8 +5015,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4858,8 +5057,8 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>4</v>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,8 +5403,11 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5230,8 +5447,8 @@
       <c r="O89" s="3">
         <v>0</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
+      <c r="P89" s="3">
+        <v>0</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>4</v>
@@ -5251,8 +5468,11 @@
       <c r="V89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,8 +5495,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5316,8 +5537,8 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>4</v>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,8 +5688,11 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5502,8 +5732,8 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>4</v>
@@ -5523,8 +5753,11 @@
       <c r="V94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,8 +6038,11 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5836,8 +6082,8 @@
       <c r="O100" s="3">
         <v>0</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>4</v>
@@ -5857,8 +6103,11 @@
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5898,8 +6147,8 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>4</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>4</v>
@@ -5919,8 +6168,11 @@
       <c r="V101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5960,8 +6212,8 @@
       <c r="O102" s="3">
         <v>0</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>4</v>
@@ -5979,6 +6231,9 @@
         <v>4</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="92">
   <si>
     <t>RERE</t>
   </si>
@@ -656,301 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>532400</v>
+        <v>577600</v>
       </c>
       <c r="E8" s="3">
-        <v>514700</v>
+        <v>519700</v>
       </c>
       <c r="F8" s="3">
-        <v>546100</v>
+        <v>505700</v>
       </c>
       <c r="G8" s="3">
-        <v>459100</v>
+        <v>546300</v>
       </c>
       <c r="H8" s="3">
-        <v>417800</v>
+        <v>446300</v>
       </c>
       <c r="I8" s="3">
-        <v>404900</v>
+        <v>408700</v>
       </c>
       <c r="J8" s="3">
+        <v>418100</v>
+      </c>
+      <c r="K8" s="3">
         <v>420300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>350400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>298300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>304700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>336300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>278900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>480800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>217500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>228900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>195400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>176200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>108400</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3">
         <v>152300</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>467900</v>
+        <v>462300</v>
       </c>
       <c r="E9" s="3">
-        <v>459300</v>
+        <v>411500</v>
       </c>
       <c r="F9" s="3">
-        <v>486500</v>
+        <v>408300</v>
       </c>
       <c r="G9" s="3">
-        <v>408700</v>
+        <v>444200</v>
       </c>
       <c r="H9" s="3">
-        <v>365800</v>
+        <v>357800</v>
       </c>
       <c r="I9" s="3">
-        <v>355100</v>
+        <v>320700</v>
       </c>
       <c r="J9" s="3">
+        <v>327900</v>
+      </c>
+      <c r="K9" s="3">
         <v>373000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>305200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>268200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>267400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>288700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>244100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>425000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>189400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>198600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>169900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>153100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>103100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>590400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>149000</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>64500</v>
+        <v>115200</v>
       </c>
       <c r="E10" s="3">
-        <v>55500</v>
+        <v>108200</v>
       </c>
       <c r="F10" s="3">
-        <v>59600</v>
+        <v>97400</v>
       </c>
       <c r="G10" s="3">
-        <v>50500</v>
+        <v>102000</v>
       </c>
       <c r="H10" s="3">
-        <v>52000</v>
+        <v>88500</v>
       </c>
       <c r="I10" s="3">
-        <v>49800</v>
+        <v>88000</v>
       </c>
       <c r="J10" s="3">
+        <v>90200</v>
+      </c>
+      <c r="K10" s="3">
         <v>47300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>45100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>30100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>37300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>47700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>34800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>55800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>28100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>30300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>25500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5200</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X10" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F12" s="3">
         <v>7000</v>
       </c>
-      <c r="E12" s="3">
-        <v>7000</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>9000</v>
       </c>
-      <c r="G12" s="3">
-        <v>5500</v>
-      </c>
       <c r="H12" s="3">
-        <v>6300</v>
+        <v>5400</v>
       </c>
       <c r="I12" s="3">
-        <v>6600</v>
+        <v>6200</v>
       </c>
       <c r="J12" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K12" s="3">
         <v>7700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>8600</v>
       </c>
       <c r="N12" s="3">
         <v>8600</v>
       </c>
       <c r="O12" s="3">
+        <v>8600</v>
+      </c>
+      <c r="P12" s="3">
         <v>9000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>19100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>22000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1115,36 +1135,36 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
+        <v>300</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>258300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
         <v>2300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1160,8 +1180,8 @@
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1169,53 +1189,56 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>8000</v>
+        <v>11900</v>
       </c>
       <c r="E15" s="3">
-        <v>9400</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>4</v>
+        <v>11500</v>
+      </c>
+      <c r="F15" s="3">
+        <v>11600</v>
       </c>
       <c r="G15" s="3">
-        <v>9400</v>
+        <v>11800</v>
       </c>
       <c r="H15" s="3">
-        <v>11000</v>
+        <v>13900</v>
       </c>
       <c r="I15" s="3">
-        <v>11100</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="3">
+        <v>14000</v>
+      </c>
+      <c r="J15" s="3">
+        <v>14800</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="3">
         <v>12300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12100</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3">
         <v>13000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>22100</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>533200</v>
+        <v>574000</v>
       </c>
       <c r="E17" s="3">
-        <v>520900</v>
+        <v>520500</v>
       </c>
       <c r="F17" s="3">
-        <v>548500</v>
+        <v>511700</v>
       </c>
       <c r="G17" s="3">
-        <v>463100</v>
+        <v>548600</v>
       </c>
       <c r="H17" s="3">
-        <v>426400</v>
+        <v>450200</v>
       </c>
       <c r="I17" s="3">
-        <v>414400</v>
+        <v>417100</v>
       </c>
       <c r="J17" s="3">
+        <v>427900</v>
+      </c>
+      <c r="K17" s="3">
         <v>733700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>365600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>321700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>323300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>356000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>300300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>568700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>233500</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V17" s="3">
         <v>139500</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-800</v>
       </c>
-      <c r="E18" s="3">
-        <v>-6100</v>
-      </c>
       <c r="F18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="G18" s="3">
         <v>-2400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H18" s="3">
-        <v>-8600</v>
+        <v>-3800</v>
       </c>
       <c r="I18" s="3">
-        <v>-9500</v>
+        <v>-8400</v>
       </c>
       <c r="J18" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="K18" s="3">
         <v>-313400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-18600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-19700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-21400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-88000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-16000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3">
         <v>-31100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,96 +1444,100 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>800</v>
+        <v>2600</v>
       </c>
       <c r="E20" s="3">
-        <v>-4900</v>
+        <v>2000</v>
       </c>
       <c r="F20" s="3">
-        <v>2000</v>
+        <v>8600</v>
       </c>
       <c r="G20" s="3">
-        <v>900</v>
+        <v>-200</v>
       </c>
       <c r="H20" s="3">
-        <v>500</v>
+        <v>4800</v>
       </c>
       <c r="I20" s="3">
-        <v>1000</v>
+        <v>2600</v>
       </c>
       <c r="J20" s="3">
         <v>200</v>
       </c>
       <c r="K20" s="3">
+        <v>200</v>
+      </c>
+      <c r="L20" s="3">
         <v>9600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
         <v>1300</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>9600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>4700</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1511,233 +1548,245 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>27200</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>-2900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>-15100</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
-        <v>400</v>
-      </c>
       <c r="I22" s="3">
+        <v>300</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>200</v>
       </c>
       <c r="L22" s="3">
+        <v>200</v>
+      </c>
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>900</v>
-      </c>
-      <c r="R22" s="3">
-        <v>700</v>
       </c>
       <c r="S22" s="3">
         <v>700</v>
       </c>
       <c r="T22" s="3">
+        <v>700</v>
+      </c>
+      <c r="U22" s="3">
         <v>1100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-700</v>
+        <v>1700</v>
       </c>
       <c r="E23" s="3">
-        <v>-11600</v>
+        <v>-2600</v>
       </c>
       <c r="F23" s="3">
-        <v>-600</v>
+        <v>-14300</v>
       </c>
       <c r="G23" s="3">
-        <v>-3300</v>
+        <v>-900</v>
       </c>
       <c r="H23" s="3">
-        <v>-8400</v>
+        <v>-7400</v>
       </c>
       <c r="I23" s="3">
-        <v>-8600</v>
+        <v>-10600</v>
       </c>
       <c r="J23" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="K23" s="3">
         <v>-313300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-23800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-20600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-89600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-13100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-15400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-17300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-30400</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X23" s="3">
         <v>-40800</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-10100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-11300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-4600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="E26" s="3">
-        <v>-10200</v>
+        <v>-1500</v>
       </c>
       <c r="F26" s="3">
-        <v>700</v>
+        <v>-12900</v>
       </c>
       <c r="G26" s="3">
-        <v>-1900</v>
+        <v>400</v>
       </c>
       <c r="H26" s="3">
-        <v>-6700</v>
+        <v>-6100</v>
       </c>
       <c r="I26" s="3">
-        <v>-6900</v>
+        <v>-8900</v>
       </c>
       <c r="J26" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-303200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-22000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-17300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-84100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13500</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V26" s="3">
         <v>-28500</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1500</v>
       </c>
-      <c r="E27" s="3">
-        <v>-13100</v>
-      </c>
       <c r="F27" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="G27" s="3">
         <v>400</v>
       </c>
-      <c r="G27" s="3">
-        <v>-6200</v>
-      </c>
       <c r="H27" s="3">
-        <v>-9100</v>
+        <v>-6100</v>
       </c>
       <c r="I27" s="3">
-        <v>-7000</v>
+        <v>-8900</v>
       </c>
       <c r="J27" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-303300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-22300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-17300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-156300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-86700</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V27" s="3">
         <v>-80200</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-800</v>
+        <v>-2600</v>
       </c>
       <c r="E32" s="3">
-        <v>4900</v>
+        <v>-2000</v>
       </c>
       <c r="F32" s="3">
-        <v>-2000</v>
+        <v>-8600</v>
       </c>
       <c r="G32" s="3">
-        <v>-900</v>
+        <v>200</v>
       </c>
       <c r="H32" s="3">
-        <v>-500</v>
+        <v>-4800</v>
       </c>
       <c r="I32" s="3">
-        <v>-1000</v>
+        <v>-2600</v>
       </c>
       <c r="J32" s="3">
         <v>-200</v>
       </c>
       <c r="K32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L32" s="3">
         <v>-9600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1300</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1500</v>
       </c>
-      <c r="E33" s="3">
-        <v>-13100</v>
-      </c>
       <c r="F33" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="G33" s="3">
         <v>400</v>
       </c>
-      <c r="G33" s="3">
-        <v>-6200</v>
-      </c>
       <c r="H33" s="3">
-        <v>-9100</v>
+        <v>-6100</v>
       </c>
       <c r="I33" s="3">
-        <v>-7000</v>
+        <v>-8900</v>
       </c>
       <c r="J33" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-303300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-22300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-17300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-156300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-86700</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V33" s="3">
         <v>-80200</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1500</v>
       </c>
-      <c r="E35" s="3">
-        <v>-13100</v>
-      </c>
       <c r="F35" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="G35" s="3">
         <v>400</v>
       </c>
-      <c r="G35" s="3">
-        <v>-6200</v>
-      </c>
       <c r="H35" s="3">
-        <v>-9100</v>
+        <v>-6100</v>
       </c>
       <c r="I35" s="3">
-        <v>-7000</v>
+        <v>-8900</v>
       </c>
       <c r="J35" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-303300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-22300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-17300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-156300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-86700</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V35" s="3">
         <v>-80200</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,56 +2657,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>231600</v>
+        <v>192100</v>
       </c>
       <c r="E41" s="3">
-        <v>227000</v>
+        <v>226100</v>
       </c>
       <c r="F41" s="3">
+        <v>223000</v>
+      </c>
+      <c r="G41" s="3">
         <v>279000</v>
       </c>
-      <c r="G41" s="3">
-        <v>201900</v>
-      </c>
       <c r="H41" s="3">
-        <v>210500</v>
+        <v>196300</v>
       </c>
       <c r="I41" s="3">
-        <v>220700</v>
+        <v>205900</v>
       </c>
       <c r="J41" s="3">
+        <v>227900</v>
+      </c>
+      <c r="K41" s="3">
         <v>240200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>175500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>169000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>155500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>187300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>269500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>396000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>94400</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2636,55 +2723,58 @@
       <c r="W41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>89900</v>
+        <v>89800</v>
       </c>
       <c r="E42" s="3">
-        <v>66600</v>
+        <v>87800</v>
       </c>
       <c r="F42" s="3">
-        <v>57900</v>
+        <v>65500</v>
       </c>
       <c r="G42" s="3">
-        <v>49100</v>
+        <v>63700</v>
       </c>
       <c r="H42" s="3">
-        <v>84400</v>
+        <v>47700</v>
       </c>
       <c r="I42" s="3">
-        <v>90800</v>
+        <v>82600</v>
       </c>
       <c r="J42" s="3">
+        <v>93800</v>
+      </c>
+      <c r="K42" s="3">
         <v>110300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>140000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>143300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>121500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>70500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>54000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>7100</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>4</v>
+      <c r="R42" s="3">
+        <v>0</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>4</v>
@@ -2701,56 +2791,59 @@
       <c r="W42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>61400</v>
+        <v>31200</v>
       </c>
       <c r="E43" s="3">
-        <v>59900</v>
+        <v>24700</v>
       </c>
       <c r="F43" s="3">
-        <v>74000</v>
+        <v>19300</v>
       </c>
       <c r="G43" s="3">
-        <v>78300</v>
+        <v>40000</v>
       </c>
       <c r="H43" s="3">
-        <v>57700</v>
+        <v>32000</v>
       </c>
       <c r="I43" s="3">
-        <v>55700</v>
+        <v>23200</v>
       </c>
       <c r="J43" s="3">
+        <v>14900</v>
+      </c>
+      <c r="K43" s="3">
         <v>96100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>71100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>67600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>99100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>112600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>83400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>70600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>65800</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2766,56 +2859,59 @@
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>93100</v>
+        <v>96700</v>
       </c>
       <c r="E44" s="3">
-        <v>119500</v>
+        <v>90800</v>
       </c>
       <c r="F44" s="3">
+        <v>117400</v>
+      </c>
+      <c r="G44" s="3">
         <v>143400</v>
       </c>
-      <c r="G44" s="3">
-        <v>94800</v>
-      </c>
       <c r="H44" s="3">
-        <v>103700</v>
+        <v>92200</v>
       </c>
       <c r="I44" s="3">
-        <v>82200</v>
+        <v>101400</v>
       </c>
       <c r="J44" s="3">
+        <v>84900</v>
+      </c>
+      <c r="K44" s="3">
         <v>61100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>62700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>93600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>92200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>66100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>71100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>50100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>45600</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2831,56 +2927,59 @@
       <c r="W44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>117400</v>
+        <v>141900</v>
       </c>
       <c r="E45" s="3">
-        <v>122100</v>
+        <v>117900</v>
       </c>
       <c r="F45" s="3">
-        <v>83900</v>
+        <v>127300</v>
       </c>
       <c r="G45" s="3">
-        <v>114700</v>
+        <v>82600</v>
       </c>
       <c r="H45" s="3">
-        <v>95600</v>
+        <v>126500</v>
       </c>
       <c r="I45" s="3">
-        <v>85700</v>
+        <v>97800</v>
       </c>
       <c r="J45" s="3">
+        <v>131200</v>
+      </c>
+      <c r="K45" s="3">
         <v>40700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>95400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>96900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>107300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>136700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>117000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>79900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>63100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2896,56 +2995,59 @@
       <c r="W45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>593400</v>
+        <v>570500</v>
       </c>
       <c r="E46" s="3">
+        <v>579200</v>
+      </c>
+      <c r="F46" s="3">
+        <v>584600</v>
+      </c>
+      <c r="G46" s="3">
+        <v>638400</v>
+      </c>
+      <c r="H46" s="3">
+        <v>523800</v>
+      </c>
+      <c r="I46" s="3">
+        <v>539800</v>
+      </c>
+      <c r="J46" s="3">
+        <v>552700</v>
+      </c>
+      <c r="K46" s="3">
+        <v>548400</v>
+      </c>
+      <c r="L46" s="3">
+        <v>544700</v>
+      </c>
+      <c r="M46" s="3">
+        <v>570500</v>
+      </c>
+      <c r="N46" s="3">
+        <v>575700</v>
+      </c>
+      <c r="O46" s="3">
+        <v>573100</v>
+      </c>
+      <c r="P46" s="3">
         <v>595100</v>
       </c>
-      <c r="F46" s="3">
-        <v>638200</v>
-      </c>
-      <c r="G46" s="3">
-        <v>538800</v>
-      </c>
-      <c r="H46" s="3">
-        <v>551900</v>
-      </c>
-      <c r="I46" s="3">
-        <v>535300</v>
-      </c>
-      <c r="J46" s="3">
-        <v>548400</v>
-      </c>
-      <c r="K46" s="3">
-        <v>544700</v>
-      </c>
-      <c r="L46" s="3">
-        <v>570500</v>
-      </c>
-      <c r="M46" s="3">
-        <v>575700</v>
-      </c>
-      <c r="N46" s="3">
-        <v>573100</v>
-      </c>
-      <c r="O46" s="3">
-        <v>595100</v>
-      </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>603700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>268800</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2961,56 +3063,59 @@
       <c r="W46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>78200</v>
+        <v>79600</v>
       </c>
       <c r="E47" s="3">
-        <v>68000</v>
+        <v>76300</v>
       </c>
       <c r="F47" s="3">
+        <v>66800</v>
+      </c>
+      <c r="G47" s="3">
         <v>65900</v>
       </c>
-      <c r="G47" s="3">
-        <v>66200</v>
-      </c>
       <c r="H47" s="3">
-        <v>68400</v>
+        <v>64300</v>
       </c>
       <c r="I47" s="3">
-        <v>69600</v>
+        <v>66900</v>
       </c>
       <c r="J47" s="3">
+        <v>71800</v>
+      </c>
+      <c r="K47" s="3">
         <v>31000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>31700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>32600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>32800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>33400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>29200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>16200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>15100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3026,56 +3131,59 @@
       <c r="W47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>20500</v>
+        <v>22700</v>
       </c>
       <c r="E48" s="3">
-        <v>21200</v>
+        <v>20000</v>
       </c>
       <c r="F48" s="3">
+        <v>20800</v>
+      </c>
+      <c r="G48" s="3">
         <v>20900</v>
       </c>
-      <c r="G48" s="3">
-        <v>18500</v>
-      </c>
       <c r="H48" s="3">
-        <v>17100</v>
+        <v>18000</v>
       </c>
       <c r="I48" s="3">
-        <v>15800</v>
+        <v>16700</v>
       </c>
       <c r="J48" s="3">
+        <v>16300</v>
+      </c>
+      <c r="K48" s="3">
         <v>16700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9300</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3091,56 +3199,59 @@
       <c r="W48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>20700</v>
+        <v>14300</v>
       </c>
       <c r="E49" s="3">
-        <v>28700</v>
+        <v>20200</v>
       </c>
       <c r="F49" s="3">
+        <v>28200</v>
+      </c>
+      <c r="G49" s="3">
         <v>38200</v>
       </c>
-      <c r="G49" s="3">
-        <v>47600</v>
-      </c>
       <c r="H49" s="3">
-        <v>57000</v>
+        <v>46300</v>
       </c>
       <c r="I49" s="3">
-        <v>66900</v>
+        <v>55800</v>
       </c>
       <c r="J49" s="3">
+        <v>69100</v>
+      </c>
+      <c r="K49" s="3">
         <v>76800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>366500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>380000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>386400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>397600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>421200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>432800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>444300</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,56 +3403,59 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>9500</v>
+        <v>21300</v>
       </c>
       <c r="E52" s="3">
-        <v>16100</v>
+        <v>9200</v>
       </c>
       <c r="F52" s="3">
+        <v>15800</v>
+      </c>
+      <c r="G52" s="3">
         <v>11300</v>
       </c>
-      <c r="G52" s="3">
-        <v>10900</v>
-      </c>
       <c r="H52" s="3">
-        <v>11600</v>
+        <v>10600</v>
       </c>
       <c r="I52" s="3">
-        <v>12400</v>
+        <v>11400</v>
       </c>
       <c r="J52" s="3">
+        <v>12800</v>
+      </c>
+      <c r="K52" s="3">
         <v>38900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>20500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2400</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,56 +3539,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>722200</v>
+        <v>708400</v>
       </c>
       <c r="E54" s="3">
-        <v>729100</v>
+        <v>705000</v>
       </c>
       <c r="F54" s="3">
-        <v>774400</v>
+        <v>716200</v>
       </c>
       <c r="G54" s="3">
-        <v>681900</v>
+        <v>774700</v>
       </c>
       <c r="H54" s="3">
-        <v>706000</v>
+        <v>662900</v>
       </c>
       <c r="I54" s="3">
-        <v>699900</v>
+        <v>690500</v>
       </c>
       <c r="J54" s="3">
+        <v>722700</v>
+      </c>
+      <c r="K54" s="3">
         <v>711800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>973600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1011900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1023500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1036000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1078300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1077800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>739900</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3481,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,56 +3661,57 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F57" s="3">
+        <v>18500</v>
+      </c>
+      <c r="G57" s="3">
+        <v>75100</v>
+      </c>
+      <c r="H57" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I57" s="3">
+        <v>9700</v>
+      </c>
+      <c r="J57" s="3">
+        <v>12300</v>
+      </c>
+      <c r="K57" s="3">
         <v>10300</v>
       </c>
-      <c r="E57" s="3">
-        <v>18900</v>
-      </c>
-      <c r="F57" s="3">
-        <v>75000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>16400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>9900</v>
-      </c>
-      <c r="I57" s="3">
-        <v>11900</v>
-      </c>
-      <c r="J57" s="3">
-        <v>10300</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6300</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3596,56 +3727,59 @@
       <c r="W57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>65600</v>
+        <v>43800</v>
       </c>
       <c r="E58" s="3">
-        <v>79000</v>
+        <v>64000</v>
       </c>
       <c r="F58" s="3">
-        <v>49300</v>
+        <v>77600</v>
       </c>
       <c r="G58" s="3">
-        <v>28200</v>
+        <v>54100</v>
       </c>
       <c r="H58" s="3">
-        <v>39300</v>
+        <v>27400</v>
       </c>
       <c r="I58" s="3">
-        <v>45000</v>
+        <v>38500</v>
       </c>
       <c r="J58" s="3">
+        <v>46400</v>
+      </c>
+      <c r="K58" s="3">
         <v>17500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>20300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>21300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>20200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>29700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>63500</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3661,56 +3795,59 @@
       <c r="W58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>122700</v>
+        <v>28200</v>
       </c>
       <c r="E59" s="3">
-        <v>102400</v>
+        <v>42600</v>
       </c>
       <c r="F59" s="3">
-        <v>114100</v>
+        <v>23900</v>
       </c>
       <c r="G59" s="3">
-        <v>95900</v>
+        <v>88800</v>
       </c>
       <c r="H59" s="3">
-        <v>108800</v>
+        <v>26600</v>
       </c>
       <c r="I59" s="3">
-        <v>86200</v>
+        <v>45700</v>
       </c>
       <c r="J59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="K59" s="3">
         <v>116300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>99500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>114800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>106100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>95000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>83000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>77700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>85300</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3726,56 +3863,59 @@
       <c r="W59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>198600</v>
+        <v>176400</v>
       </c>
       <c r="E60" s="3">
-        <v>200200</v>
+        <v>193900</v>
       </c>
       <c r="F60" s="3">
+        <v>196700</v>
+      </c>
+      <c r="G60" s="3">
         <v>238500</v>
       </c>
-      <c r="G60" s="3">
-        <v>140600</v>
-      </c>
       <c r="H60" s="3">
-        <v>158000</v>
+        <v>136600</v>
       </c>
       <c r="I60" s="3">
-        <v>143100</v>
+        <v>154500</v>
       </c>
       <c r="J60" s="3">
+        <v>147800</v>
+      </c>
+      <c r="K60" s="3">
         <v>144100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>117800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>144400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>137800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>113900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>110100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>114300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>155100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3791,31 +3931,34 @@
       <c r="W60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>11500</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3830,17 +3973,17 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3200</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3856,56 +3999,59 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>9000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>10600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>12700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>13800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>14900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>17400</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>20400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>30600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>32400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>33900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>35600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>46600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>52600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>46300</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,56 +4271,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>207600</v>
+        <v>193900</v>
       </c>
       <c r="E66" s="3">
-        <v>210900</v>
+        <v>202700</v>
       </c>
       <c r="F66" s="3">
-        <v>251200</v>
+        <v>207100</v>
       </c>
       <c r="G66" s="3">
-        <v>154300</v>
+        <v>251300</v>
       </c>
       <c r="H66" s="3">
-        <v>172900</v>
+        <v>150000</v>
       </c>
       <c r="I66" s="3">
-        <v>160500</v>
+        <v>169100</v>
       </c>
       <c r="J66" s="3">
+        <v>165700</v>
+      </c>
+      <c r="K66" s="3">
         <v>164500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>148400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>176800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>171700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>149400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>157500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>168900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>204600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4381,11 +4549,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>1370500</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,8 +4637,11 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4477,11 +4651,11 @@
       <c r="E72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F72" s="3">
-        <v>-1291800</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-1292200</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>4</v>
@@ -4489,33 +4663,33 @@
       <c r="I72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1269800</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>-902900</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>-835500</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,56 +4909,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>514600</v>
+        <v>514500</v>
       </c>
       <c r="E76" s="3">
-        <v>518200</v>
+        <v>502300</v>
       </c>
       <c r="F76" s="3">
-        <v>523200</v>
+        <v>509100</v>
       </c>
       <c r="G76" s="3">
-        <v>527600</v>
+        <v>523400</v>
       </c>
       <c r="H76" s="3">
-        <v>533100</v>
+        <v>512800</v>
       </c>
       <c r="I76" s="3">
-        <v>539400</v>
+        <v>521400</v>
       </c>
       <c r="J76" s="3">
+        <v>557000</v>
+      </c>
+      <c r="K76" s="3">
         <v>547200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>825200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>835000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>851800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>886500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>920700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>908900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-835200</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4791,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1500</v>
       </c>
-      <c r="E81" s="3">
-        <v>-13100</v>
-      </c>
       <c r="F81" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="G81" s="3">
         <v>400</v>
       </c>
-      <c r="G81" s="3">
-        <v>-6200</v>
-      </c>
       <c r="H81" s="3">
-        <v>-9100</v>
+        <v>-6100</v>
       </c>
       <c r="I81" s="3">
-        <v>-7000</v>
+        <v>-8900</v>
       </c>
       <c r="J81" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-303300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-22300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-17300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-156300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-86700</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V81" s="3">
         <v>-80200</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,31 +5214,32 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5060,8 +5259,8 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>4</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>4</v>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,31 +5620,34 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -5450,8 +5667,8 @@
       <c r="P89" s="3">
         <v>0</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>4</v>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>4</v>
@@ -5471,8 +5688,11 @@
       <c r="W89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,31 +5716,32 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5540,8 +5761,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,31 +5918,34 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -5735,8 +5965,8 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>4</v>
@@ -5756,8 +5986,11 @@
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,31 +6014,32 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,31 +6284,34 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -6085,8 +6331,8 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>4</v>
@@ -6106,31 +6352,34 @@
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6150,8 +6399,8 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>4</v>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>4</v>
@@ -6171,8 +6420,11 @@
       <c r="W101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6215,8 +6467,8 @@
       <c r="P102" s="3">
         <v>0</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>4</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>4</v>
@@ -6234,6 +6486,9 @@
         <v>4</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="92">
   <si>
     <t>RERE</t>
   </si>
@@ -656,314 +656,326 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>664400</v>
+      </c>
+      <c r="E8" s="3">
         <v>577600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>519700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>505700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>546300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>446300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>408700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>418100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>420300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>350400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>298300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>304700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>336300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>278900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>480800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>217500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>228900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>195400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>176200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>108400</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="3">
         <v>152300</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>535000</v>
+      </c>
+      <c r="E9" s="3">
         <v>462300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>411500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>408300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>444200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>357800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>320700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>327900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>373000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>305200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>268200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>267400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>288700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>244100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>425000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>189400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>198600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>169900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>153100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>103100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>590400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>149000</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>129400</v>
+      </c>
+      <c r="E10" s="3">
         <v>115200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>108200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>97400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>102000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>88500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>88000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>90200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>47300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>45100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>30100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>37300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>47700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>34800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>55800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>28100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>30300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>25500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5200</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,76 +1000,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E12" s="3">
         <v>7600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8100</v>
-      </c>
-      <c r="N12" s="3">
-        <v>8600</v>
       </c>
       <c r="O12" s="3">
         <v>8600</v>
       </c>
       <c r="P12" s="3">
+        <v>8600</v>
+      </c>
+      <c r="Q12" s="3">
         <v>9000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>22000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1140,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1138,36 +1157,36 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>258300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
         <v>2300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1183,8 +1202,8 @@
       <c r="U14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1192,56 +1211,59 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E15" s="3">
         <v>11900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14800</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3">
         <v>12300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12100</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3">
         <v>13000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>22100</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1260,8 +1282,11 @@
       <c r="X15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1308,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>657100</v>
+      </c>
+      <c r="E17" s="3">
         <v>574000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>520500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>511700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>548600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>450200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>417100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>427900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>733700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>365600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>321700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>323300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>356000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>300300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>568700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>233500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W17" s="3">
         <v>139500</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E18" s="3">
         <v>3500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-313400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-23400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-18600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-21400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-88000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-16000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W18" s="3">
         <v>-31100</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,103 +1477,107 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
       </c>
       <c r="L20" s="3">
+        <v>200</v>
+      </c>
+      <c r="M20" s="3">
         <v>9600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W20" s="3">
         <v>1300</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E21" s="3">
         <v>12900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4700</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1551,242 +1587,254 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3">
         <v>27200</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
         <v>-2900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3">
         <v>-15100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>400</v>
+      </c>
+      <c r="E22" s="3">
         <v>500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>200</v>
-      </c>
-      <c r="H22" s="3">
-        <v>300</v>
       </c>
       <c r="I22" s="3">
         <v>300</v>
       </c>
       <c r="J22" s="3">
+        <v>300</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>200</v>
       </c>
       <c r="L22" s="3">
         <v>200</v>
       </c>
       <c r="M22" s="3">
+        <v>200</v>
+      </c>
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>900</v>
-      </c>
-      <c r="S22" s="3">
-        <v>700</v>
       </c>
       <c r="T22" s="3">
         <v>700</v>
       </c>
       <c r="U22" s="3">
+        <v>700</v>
+      </c>
+      <c r="V22" s="3">
         <v>1100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-313300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-23800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-24700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-89600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-13100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-15400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-17300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-30400</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-40800</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-10100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-11300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-4600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E26" s="3">
         <v>2500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-303200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-22000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-84100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-13500</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W26" s="3">
         <v>-28500</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E27" s="3">
         <v>2500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-303300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-22300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-156300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-86700</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W27" s="3">
         <v>-80200</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2327,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
       </c>
       <c r="L32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M32" s="3">
         <v>-9600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W32" s="3">
         <v>-1300</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E33" s="3">
         <v>2500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-303300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-22300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-156300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-86700</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W33" s="3">
         <v>-80200</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E35" s="3">
         <v>2500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-303300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-22300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-156300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-86700</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W35" s="3">
         <v>-80200</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,59 +2743,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>269900</v>
+      </c>
+      <c r="E41" s="3">
         <v>192100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>226100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>223000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>279000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>196300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>205900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>227900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>240200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>175500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>169000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>155500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>187300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>269500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>396000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>94400</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2726,58 +2812,61 @@
       <c r="X41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E42" s="3">
         <v>89800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>87800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>65500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>63700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>47700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>82600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>93800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>110300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>140000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>143300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>121500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>70500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>54000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>7100</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>4</v>
+      <c r="S42" s="3">
+        <v>0</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>4</v>
@@ -2794,59 +2883,62 @@
       <c r="X42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E43" s="3">
         <v>31200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>19300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>40000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>32000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>23200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>96100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>71100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>67600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>99100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>112600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>83400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>70600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>65800</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2862,59 +2954,62 @@
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E44" s="3">
         <v>96700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>90800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>117400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>143400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>92200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>101400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>84900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>61100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>62700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>93600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>92200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>66100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>71100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>50100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>45600</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2930,59 +3025,62 @@
       <c r="X44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>113900</v>
+      </c>
+      <c r="E45" s="3">
         <v>141900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>117900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>127300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>82600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>126500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>97800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>131200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>40700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>95400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>96900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>107300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>136700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>117000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>79900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>63100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2998,59 +3096,62 @@
       <c r="X45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>571200</v>
+      </c>
+      <c r="E46" s="3">
         <v>570500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>579200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>584600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>638400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>523800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>539800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>552700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>548400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>544700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>570500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>575700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>573100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>595100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>603700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>268800</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3066,59 +3167,62 @@
       <c r="X46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>76200</v>
+      </c>
+      <c r="E47" s="3">
         <v>79600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>76300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>66800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>65900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>64300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>66900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>71800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>31000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>31700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>32600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>32800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>33400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>29200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>16200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>15100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3134,59 +3238,62 @@
       <c r="X47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E48" s="3">
         <v>22700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>18000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>16300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9300</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3202,59 +3309,62 @@
       <c r="X48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E49" s="3">
         <v>14300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>20200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>28200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>38200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>46300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>55800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>69100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>76800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>366500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>380000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>386400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>397600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>421200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>432800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>444300</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3270,8 +3380,11 @@
       <c r="X49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,59 +3522,62 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E52" s="3">
         <v>21300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>20500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2400</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3474,8 +3593,11 @@
       <c r="X52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,59 +3664,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>697400</v>
+      </c>
+      <c r="E54" s="3">
         <v>708400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>705000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>716200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>774700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>662900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>690500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>722700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>711800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>973600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1011900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1023500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1036000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1078300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1077800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>739900</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3610,8 +3735,11 @@
       <c r="X54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,59 +3791,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E57" s="3">
         <v>15000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>75100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6300</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3730,59 +3860,62 @@
       <c r="X57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E58" s="3">
         <v>43800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>64000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>77600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>54100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>27400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>38500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>46400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>21300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>20200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>29700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>63500</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3798,59 +3931,62 @@
       <c r="X58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E59" s="3">
         <v>28200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>88800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>45700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>116300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>99500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>114800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>106100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>95000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>83000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>77700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>85300</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3866,59 +4002,62 @@
       <c r="X59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>179100</v>
+      </c>
+      <c r="E60" s="3">
         <v>176400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>193900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>196700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>238500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>136600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>154500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>147800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>144100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>117800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>144400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>137800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>113900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>110100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>114300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>155100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3934,35 +4073,38 @@
       <c r="X60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3976,17 +4118,17 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3200</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4002,8 +4144,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4028,33 +4173,33 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>20400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>30600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>32400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>33900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>35600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>46600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>52600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>46300</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4070,8 +4215,11 @@
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,59 +4428,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>191300</v>
+      </c>
+      <c r="E66" s="3">
         <v>193900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>202700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>207100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>251300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>150000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>169100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>165700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>164500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>148400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>176800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>171700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>149400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>157500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>168900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>204600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4342,8 +4499,11 @@
       <c r="X66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4552,11 +4719,11 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>1370500</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,8 +4810,11 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4654,45 +4827,45 @@
       <c r="F72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>-1292200</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>-1269800</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>-902900</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S72" s="3">
         <v>-835500</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4708,8 +4881,11 @@
       <c r="X72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,59 +5094,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>506200</v>
+      </c>
+      <c r="E76" s="3">
         <v>514500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>502300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>509100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>523400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>512800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>521400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>557000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>547200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>825200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>835000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>851800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>886500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>920700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>908900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-835200</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4980,8 +5165,11 @@
       <c r="X76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E81" s="3">
         <v>2500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-303300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-22300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-156300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-86700</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W81" s="3">
         <v>-80200</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5412,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5241,8 +5439,8 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -5262,8 +5460,8 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>4</v>
@@ -5283,8 +5481,11 @@
       <c r="X83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,8 +5836,11 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5649,8 +5865,8 @@
       <c r="J89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -5670,8 +5886,8 @@
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>4</v>
@@ -5691,8 +5907,11 @@
       <c r="X89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,8 +5936,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5743,8 +5963,8 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5764,8 +5984,8 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
@@ -5785,8 +6005,11 @@
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,8 +6147,11 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5947,8 +6176,8 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -5968,8 +6197,8 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>4</v>
@@ -5989,8 +6218,11 @@
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6041,8 +6274,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6083,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,8 +6529,11 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6313,8 +6558,8 @@
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -6334,8 +6579,8 @@
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>4</v>
@@ -6355,8 +6600,11 @@
       <c r="X100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6381,8 +6629,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6402,8 +6650,8 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>4</v>
+      <c r="R101" s="3">
+        <v>0</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>4</v>
@@ -6423,8 +6671,11 @@
       <c r="X101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6470,8 +6721,8 @@
       <c r="Q102" s="3">
         <v>0</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>4</v>
@@ -6489,6 +6740,9 @@
         <v>4</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="92">
   <si>
     <t>RERE</t>
   </si>
@@ -656,326 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>641300</v>
+      </c>
+      <c r="E8" s="3">
         <v>664400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>577600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>519700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>505700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>546300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>446300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>408700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>418100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>420300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>350400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>298300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>304700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>336300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>278900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>480800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>217500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>228900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>195400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>176200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>108400</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="3">
         <v>152300</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>498300</v>
+      </c>
+      <c r="E9" s="3">
         <v>535000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>462300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>411500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>408300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>444200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>357800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>320700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>327900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>373000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>305200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>268200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>267400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>288700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>244100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>425000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>189400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>198600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>169900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>153100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>103100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>590400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>149000</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E10" s="3">
         <v>129400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>115200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>108200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>97400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>102000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>88500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>88000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>90200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>47300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>45100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>30100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>37300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>47700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>34800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>55800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>28100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>30300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>25500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>23100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5200</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,79 +1014,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E12" s="3">
         <v>7800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8100</v>
-      </c>
-      <c r="O12" s="3">
-        <v>8600</v>
       </c>
       <c r="P12" s="3">
         <v>8600</v>
       </c>
       <c r="Q12" s="3">
+        <v>8600</v>
+      </c>
+      <c r="R12" s="3">
         <v>9000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>19100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>22000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,16 +1160,19 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3">
+        <v>4900</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
@@ -1160,11 +1180,11 @@
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
-        <v>300</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
+        <v>700</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
@@ -1172,24 +1192,24 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>258300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1205,8 +1225,8 @@
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1214,59 +1234,62 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>11400</v>
+        <v>9200</v>
       </c>
       <c r="E15" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F15" s="3">
         <v>11900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14800</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3">
         <v>12300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>12100</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3">
         <v>13000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>22100</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1285,8 +1308,11 @@
       <c r="Y15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>631300</v>
+      </c>
+      <c r="E17" s="3">
         <v>657100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>574000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>520500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>511700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>548600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>450200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>417100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>427900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>733700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>365600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>321700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>323300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>356000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>568700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>233500</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X17" s="3">
         <v>139500</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-313400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-23400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-18600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-21400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-88000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-16000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3">
         <v>-31100</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,109 +1511,113 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1600</v>
+        <v>4100</v>
       </c>
       <c r="E20" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F20" s="3">
         <v>2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8600</v>
       </c>
-      <c r="H20" s="3">
-        <v>-200</v>
-      </c>
       <c r="I20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J20" s="3">
         <v>4800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2600</v>
-      </c>
-      <c r="K20" s="3">
-        <v>200</v>
       </c>
       <c r="L20" s="3">
         <v>200</v>
       </c>
       <c r="M20" s="3">
+        <v>200</v>
+      </c>
+      <c r="N20" s="3">
         <v>9600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3">
         <v>1300</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>17100</v>
+        <v>15100</v>
       </c>
       <c r="E21" s="3">
+        <v>19700</v>
+      </c>
+      <c r="F21" s="3">
         <v>12900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3100</v>
       </c>
-      <c r="H21" s="3">
-        <v>9600</v>
-      </c>
       <c r="I21" s="3">
+        <v>9900</v>
+      </c>
+      <c r="J21" s="3">
         <v>5200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4700</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1590,251 +1627,263 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>27200</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>-2900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3">
         <v>-15100</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
         <v>400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>200</v>
-      </c>
-      <c r="I22" s="3">
-        <v>300</v>
       </c>
       <c r="J22" s="3">
         <v>300</v>
       </c>
       <c r="K22" s="3">
+        <v>300</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>200</v>
       </c>
       <c r="M22" s="3">
         <v>200</v>
       </c>
       <c r="N22" s="3">
+        <v>200</v>
+      </c>
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>900</v>
-      </c>
-      <c r="T22" s="3">
-        <v>700</v>
       </c>
       <c r="U22" s="3">
         <v>700</v>
       </c>
       <c r="V22" s="3">
+        <v>700</v>
+      </c>
+      <c r="W22" s="3">
         <v>1100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E23" s="3">
         <v>6200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-313300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-23800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-89600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-13100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-15400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-17300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-30400</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-40800</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-4400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-10100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-5500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E26" s="3">
         <v>10600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-303200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-17000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-22000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-84100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-13500</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X26" s="3">
         <v>-28500</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E27" s="3">
         <v>10600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-303300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-17400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-22300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-17300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-156300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-86700</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X27" s="3">
         <v>-80200</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,150 +2397,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1600</v>
+        <v>-4100</v>
       </c>
       <c r="E32" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8600</v>
       </c>
-      <c r="H32" s="3">
-        <v>200</v>
-      </c>
       <c r="I32" s="3">
+        <v>500</v>
+      </c>
+      <c r="J32" s="3">
         <v>-4800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2600</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-200</v>
       </c>
       <c r="L32" s="3">
         <v>-200</v>
       </c>
       <c r="M32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N32" s="3">
         <v>-9600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3">
         <v>-1300</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E33" s="3">
         <v>10600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-303300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-17400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-22300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-17300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-156300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-86700</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X33" s="3">
         <v>-80200</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E35" s="3">
         <v>10600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-303300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-17400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-22300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-17300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-156300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-86700</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X35" s="3">
         <v>-80200</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,62 +2830,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>249300</v>
+      </c>
+      <c r="E41" s="3">
         <v>269900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>192100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>226100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>223000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>279000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>196300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>205900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>227900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>240200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>175500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>169000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>155500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>187300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>269500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>396000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>94400</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2815,61 +2902,64 @@
       <c r="Y41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>80000</v>
+        <v>79600</v>
       </c>
       <c r="E42" s="3">
+        <v>88200</v>
+      </c>
+      <c r="F42" s="3">
         <v>89800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>87800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>65500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>63700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>47700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>82600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>93800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>110300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>140000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>143300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>121500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>70500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>54000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>7100</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>4</v>
+      <c r="T42" s="3">
+        <v>0</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>4</v>
@@ -2886,62 +2976,65 @@
       <c r="Y42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>16100</v>
+        <v>34900</v>
       </c>
       <c r="E43" s="3">
+        <v>59700</v>
+      </c>
+      <c r="F43" s="3">
         <v>31200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>19300</v>
       </c>
-      <c r="H43" s="3">
-        <v>40000</v>
-      </c>
       <c r="I43" s="3">
+        <v>57300</v>
+      </c>
+      <c r="J43" s="3">
         <v>32000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>23200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>96100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>71100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>67600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>99100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>112600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>83400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>70600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>65800</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2957,62 +3050,65 @@
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>101500</v>
+      </c>
+      <c r="E44" s="3">
         <v>73300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>96700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>90800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>117400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>143400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>92200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>101400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>84900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>61100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>62700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>93600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>92200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>66100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>71100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>50100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>45600</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3028,62 +3124,65 @@
       <c r="Y44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>113900</v>
+        <v>136900</v>
       </c>
       <c r="E45" s="3">
+        <v>62000</v>
+      </c>
+      <c r="F45" s="3">
         <v>141900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>117900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>127300</v>
       </c>
-      <c r="H45" s="3">
-        <v>82600</v>
-      </c>
       <c r="I45" s="3">
+        <v>65300</v>
+      </c>
+      <c r="J45" s="3">
         <v>126500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>97800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>131200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>40700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>95400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>96900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>107300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>136700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>117000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>79900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>63100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3099,62 +3198,65 @@
       <c r="Y45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>616000</v>
+      </c>
+      <c r="E46" s="3">
         <v>571200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>570500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>579200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>584600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>638400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>523800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>539800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>552700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>548400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>544700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>570500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>575700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>573100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>595100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>603700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>268800</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3170,62 +3272,65 @@
       <c r="Y46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E47" s="3">
         <v>76200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>79600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>76300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>66800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>65900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>64300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>66900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>71800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>31000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>31700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>32600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>32800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>33400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>29200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>16200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>15100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3241,62 +3346,65 @@
       <c r="Y47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>21400</v>
+        <v>24400</v>
       </c>
       <c r="E48" s="3">
+        <v>39000</v>
+      </c>
+      <c r="F48" s="3">
         <v>22700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20800</v>
       </c>
-      <c r="H48" s="3">
-        <v>20900</v>
-      </c>
       <c r="I48" s="3">
+        <v>28800</v>
+      </c>
+      <c r="J48" s="3">
         <v>18000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>16700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9300</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3312,62 +3420,65 @@
       <c r="Y48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E49" s="3">
         <v>7800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>20200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>28200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>38200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>46300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>55800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>69100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>76800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>366500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>380000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>386400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>397600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>421200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>432800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>444300</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3383,8 +3494,11 @@
       <c r="Y49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,62 +3642,65 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>20800</v>
+        <v>21400</v>
       </c>
       <c r="E52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F52" s="3">
         <v>21300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15800</v>
       </c>
-      <c r="H52" s="3">
-        <v>11300</v>
-      </c>
       <c r="I52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J52" s="3">
         <v>10600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>38900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>17600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>20500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>13900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2400</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3596,8 +3716,11 @@
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,62 +3790,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>738100</v>
+      </c>
+      <c r="E54" s="3">
         <v>697400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>708400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>705000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>716200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>774700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>662900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>690500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>722700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>711800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>973600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1011900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1023500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1036000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1078300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1077800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>739900</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3738,8 +3864,11 @@
       <c r="Y54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,62 +3922,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E57" s="3">
         <v>23500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>75100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6300</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3863,62 +3994,65 @@
       <c r="Y57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>30800</v>
+        <v>38700</v>
       </c>
       <c r="E58" s="3">
+        <v>37700</v>
+      </c>
+      <c r="F58" s="3">
         <v>43800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>64000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>77600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>54100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>27400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>38500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>46400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>20300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>21300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>20200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>29700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>63500</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3934,62 +4068,65 @@
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>28600</v>
+        <v>50700</v>
       </c>
       <c r="E59" s="3">
+        <v>93300</v>
+      </c>
+      <c r="F59" s="3">
         <v>28200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>42600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>88800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>45700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>116300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>99500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>114800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>106100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>95000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>83000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>77700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>85300</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4005,62 +4142,65 @@
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>211200</v>
+      </c>
+      <c r="E60" s="3">
         <v>179100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>176400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>193900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>196700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>238500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>136600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>154500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>147800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>144100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>117800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>144400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>137800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>113900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>110100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>114300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>155100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4076,38 +4216,41 @@
       <c r="Y60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E61" s="3">
         <v>11000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4121,17 +4264,17 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3200</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4147,8 +4290,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4176,33 +4322,33 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>20400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>30600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>32400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>33900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>35600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>46600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>52600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>46300</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4218,8 +4364,11 @@
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,62 +4586,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>222400</v>
+      </c>
+      <c r="E66" s="3">
         <v>191300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>193900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>202700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>207100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>251300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>150000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>169100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>165700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>164500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>148400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>176800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>171700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>149400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>157500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>168900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>204600</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4502,8 +4660,11 @@
       <c r="Y66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4722,11 +4890,11 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>1370500</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4742,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,16 +4984,19 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>4</v>
+      <c r="E72" s="3">
+        <v>-1256500</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>4</v>
@@ -4830,45 +5004,45 @@
       <c r="G72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3">
         <v>-1292200</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-1269800</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-902900</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T72" s="3">
         <v>-835500</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>4</v>
       </c>
@@ -4884,8 +5058,11 @@
       <c r="Y72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,62 +5280,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>515600</v>
+      </c>
+      <c r="E76" s="3">
         <v>506200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>514500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>502300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>509100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>523400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>512800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>521400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>557000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>547200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>825200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>835000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>851800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>886500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>920700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>908900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-835200</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5168,8 +5354,11 @@
       <c r="Y76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E81" s="3">
         <v>10600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-303300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-17400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-22300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-17300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-156300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-86700</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X81" s="3">
         <v>-80200</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,8 +5611,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5442,8 +5641,8 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -5463,8 +5662,8 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>4</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>4</v>
@@ -5484,8 +5683,11 @@
       <c r="Y83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,8 +6053,11 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5868,8 +6085,8 @@
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -5889,8 +6106,8 @@
       <c r="R89" s="3">
         <v>0</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>4</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>4</v>
@@ -5910,8 +6127,11 @@
       <c r="Y89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,8 +6157,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5966,8 +6187,8 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5987,8 +6208,8 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
@@ -6008,8 +6229,11 @@
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,8 +6377,11 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6179,8 +6409,8 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -6200,8 +6430,8 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>4</v>
@@ -6221,8 +6451,11 @@
       <c r="Y94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6277,8 +6511,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,8 +6775,11 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6561,8 +6807,8 @@
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -6582,8 +6828,8 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>4</v>
@@ -6603,8 +6849,11 @@
       <c r="Y100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6632,8 +6881,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6653,8 +6902,8 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>4</v>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>4</v>
@@ -6674,31 +6923,34 @@
       <c r="Y101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -6724,8 +6976,8 @@
       <c r="R102" s="3">
         <v>0</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>4</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>4</v>
@@ -6743,6 +6995,9 @@
         <v>4</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RERE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="92">
   <si>
     <t>RERE</t>
   </si>
@@ -656,339 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
         <v>641300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>664400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>577600</v>
       </c>
-      <c r="G8" s="3">
-        <v>519700</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3">
         <v>505700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>546300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>446300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>408700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>418100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>420300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>350400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>298300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>304700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>336300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>278900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>480800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>217500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>228900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>195400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>176200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>108400</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="3">
+      <c r="Z8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="3">
         <v>152300</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3">
         <v>498300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>535000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>462300</v>
       </c>
-      <c r="G9" s="3">
-        <v>411500</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="3">
         <v>408300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>444200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>357800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>320700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>327900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>373000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>305200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>268200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>267400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>288700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>244100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>425000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>189400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>198600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>169900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>153100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>103100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>590400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>149000</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3">
         <v>143000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>129400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>115200</v>
       </c>
-      <c r="G10" s="3">
-        <v>108200</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="3">
         <v>97400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>102000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>88500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>88000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>90200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>47300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>45100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>30100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>37300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>47700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>34800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>55800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>28100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>30300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>25500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>23100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5200</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA10" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,82 +1028,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3">
         <v>7600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>9000</v>
+      </c>
+      <c r="K12" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="M12" s="3">
         <v>6900</v>
       </c>
-      <c r="H12" s="3">
-        <v>7000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>9000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>5400</v>
-      </c>
-      <c r="K12" s="3">
-        <v>6200</v>
-      </c>
-      <c r="L12" s="3">
-        <v>6900</v>
-      </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>8100</v>
-      </c>
-      <c r="P12" s="3">
-        <v>8600</v>
       </c>
       <c r="Q12" s="3">
         <v>8600</v>
       </c>
       <c r="R12" s="3">
+        <v>8600</v>
+      </c>
+      <c r="S12" s="3">
         <v>9000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>19100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>22000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,56 +1180,59 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>4900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
         <v>258300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
         <v>2300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1228,8 +1248,8 @@
       <c r="W14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1237,62 +1257,65 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>9200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11900</v>
       </c>
-      <c r="G15" s="3">
-        <v>11500</v>
-      </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>11600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>13900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>14800</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3">
         <v>12300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>12900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>12100</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3">
         <v>13000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>22100</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>4</v>
       </c>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="3">
         <v>631300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>657100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>574000</v>
       </c>
-      <c r="G17" s="3">
-        <v>520500</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="3">
         <v>511700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>548600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>450200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>417100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>427900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>733700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>365600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>321700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>323300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>356000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>568700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>233500</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y17" s="3">
         <v>139500</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3">
         <v>10000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="3">
         <v>-6000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-313400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-23400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-19700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-21400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-88000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-16000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,115 +1545,119 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
         <v>4100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2600</v>
       </c>
-      <c r="G20" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
         <v>8600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>200</v>
       </c>
       <c r="M20" s="3">
         <v>200</v>
       </c>
       <c r="N20" s="3">
+        <v>200</v>
+      </c>
+      <c r="O20" s="3">
         <v>9600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="3">
         <v>1300</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>15100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12900</v>
       </c>
-      <c r="G21" s="3">
-        <v>8800</v>
-      </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>-3100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4700</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1630,260 +1667,272 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>27200</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
         <v>-2900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-15100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
-        <v>700</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3">
         <v>600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>200</v>
-      </c>
-      <c r="J22" s="3">
-        <v>300</v>
       </c>
       <c r="K22" s="3">
         <v>300</v>
       </c>
       <c r="L22" s="3">
+        <v>300</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
-      </c>
-      <c r="M22" s="3">
-        <v>200</v>
       </c>
       <c r="N22" s="3">
         <v>200</v>
       </c>
       <c r="O22" s="3">
+        <v>200</v>
+      </c>
+      <c r="P22" s="3">
         <v>300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>900</v>
-      </c>
-      <c r="U22" s="3">
-        <v>700</v>
       </c>
       <c r="V22" s="3">
         <v>700</v>
       </c>
       <c r="W22" s="3">
+        <v>700</v>
+      </c>
+      <c r="X22" s="3">
         <v>1100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3">
         <v>6800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1700</v>
       </c>
-      <c r="G23" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="3">
         <v>-14300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-313300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-23800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-20600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-89600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-13100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-15400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-17300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-30400</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-40800</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-4400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-800</v>
       </c>
-      <c r="G24" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3">
         <v>-1400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-10100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-11300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-5500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3">
         <v>5900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2500</v>
       </c>
-      <c r="G26" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I26" s="3">
         <v>-12900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-303200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-17000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-84100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-13500</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-28500</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3">
         <v>5900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2500</v>
       </c>
-      <c r="G27" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I27" s="3">
         <v>-12900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-303300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-17400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-22300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-156300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-86700</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-80200</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
         <v>-8600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-200</v>
       </c>
       <c r="M32" s="3">
         <v>-200</v>
       </c>
       <c r="N32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O32" s="3">
         <v>-9600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3">
         <v>5900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2500</v>
       </c>
-      <c r="G33" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="3">
         <v>-12900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-303300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-17400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-22300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-156300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-86700</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-80200</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3">
         <v>5900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2500</v>
       </c>
-      <c r="G35" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="3">
         <v>-12900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-303300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-17400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-22300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-156300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-86700</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-80200</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,65 +2917,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="3">
         <v>249300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>269900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>192100</v>
       </c>
-      <c r="G41" s="3">
-        <v>226100</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3">
         <v>223000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>279000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>196300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>205900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>227900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>240200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>175500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>169000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>155500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>187300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>269500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>396000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>94400</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2905,64 +2992,67 @@
       <c r="Z41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>79600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>88200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>89800</v>
       </c>
-      <c r="G42" s="3">
-        <v>87800</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>65500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>63700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>47700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>82600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>93800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>110300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>140000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>143300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>121500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>70500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>54000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>7100</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>4</v>
+      <c r="U42" s="3">
+        <v>0</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>4</v>
@@ -2979,65 +3069,68 @@
       <c r="Z42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3">
         <v>34900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>59700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>31200</v>
       </c>
-      <c r="G43" s="3">
-        <v>24700</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3">
         <v>19300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>57300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>32000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>96100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>71100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>67600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>99100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>112600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>83400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>70600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>65800</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3053,65 +3146,68 @@
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3">
         <v>101500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>73300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>96700</v>
       </c>
-      <c r="G44" s="3">
-        <v>90800</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3">
         <v>117400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>143400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>92200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>101400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>84900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>61100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>62700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>93600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>92200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>66100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>71100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>50100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>45600</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3127,65 +3223,68 @@
       <c r="Z44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3">
         <v>136900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>62000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>141900</v>
       </c>
-      <c r="G45" s="3">
-        <v>117900</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
         <v>127300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>65300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>126500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>97800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>131200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>40700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>95400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>96900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>107300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>136700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>117000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>79900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>63100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3201,65 +3300,68 @@
       <c r="Z45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="3">
         <v>616000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>571200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>570500</v>
       </c>
-      <c r="G46" s="3">
-        <v>579200</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3">
         <v>584600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>638400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>523800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>539800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>552700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>548400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>544700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>570500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>575700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>573100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>595100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>603700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>268800</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>4</v>
       </c>
@@ -3275,65 +3377,68 @@
       <c r="Z46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3">
         <v>72100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>76200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>79600</v>
       </c>
-      <c r="G47" s="3">
-        <v>76300</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3">
         <v>66800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>65900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>64300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>66900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>71800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>31000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>31700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>32600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>32800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>33400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>29200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>16200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>15100</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3349,65 +3454,68 @@
       <c r="Z47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="3">
         <v>24400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22700</v>
       </c>
-      <c r="G48" s="3">
-        <v>20000</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3">
         <v>20800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>18000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9300</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>4</v>
       </c>
@@ -3423,65 +3531,68 @@
       <c r="Z48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="3">
         <v>4200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14300</v>
       </c>
-      <c r="G49" s="3">
-        <v>20200</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="3">
         <v>28200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>38200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>46300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>55800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>69100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>76800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>366500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>380000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>386400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>397600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>421200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>432800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>444300</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>4</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,65 +3762,68 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3">
         <v>21400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21300</v>
       </c>
-      <c r="G52" s="3">
-        <v>9200</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3">
         <v>15800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>38900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>20500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>13900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2400</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,65 +3916,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="3">
         <v>738100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>697400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>708400</v>
       </c>
-      <c r="G54" s="3">
-        <v>705000</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="3">
         <v>716200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>774700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>662900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>690500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>722700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>711800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>973600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1011900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1023500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1036000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1078300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1077800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>739900</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3867,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,65 +4053,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="3">
         <v>21000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>23500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15000</v>
       </c>
-      <c r="G57" s="3">
-        <v>10100</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3">
         <v>18500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>75100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6300</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3997,65 +4128,68 @@
       <c r="Z57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" s="3">
         <v>38700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>37700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>43800</v>
       </c>
-      <c r="G58" s="3">
-        <v>64000</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I58" s="3">
         <v>77600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>54100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>27400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>38500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>46400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>17500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>20300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>21300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>13100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>20200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>29700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>63500</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4071,65 +4205,68 @@
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
         <v>50700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>93300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28200</v>
       </c>
-      <c r="G59" s="3">
-        <v>42600</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
         <v>23900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>88800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>26600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>45700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>116300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>99500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>114800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>106100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>95000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>83000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>77700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>85300</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4145,65 +4282,68 @@
       <c r="Z59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E60" s="3">
         <v>211200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>179100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>176400</v>
       </c>
-      <c r="G60" s="3">
-        <v>193900</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3">
         <v>196700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>238500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>136600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>154500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>147800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>144100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>117800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>144400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>137800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>113900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>110100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>114300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>155100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>4</v>
       </c>
@@ -4219,41 +4359,44 @@
       <c r="Z60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>10500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11500</v>
       </c>
-      <c r="G61" s="3">
-        <v>2100</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>2500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3400</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4267,17 +4410,17 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3200</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4293,8 +4436,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4325,33 +4471,33 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>20400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>30600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>32400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>33900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>35600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>46600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>52600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>46300</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,65 +4744,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="3">
         <v>222400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>191300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>193900</v>
       </c>
-      <c r="G66" s="3">
-        <v>202700</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3">
         <v>207100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>251300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>150000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>169100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>165700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>164500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>148400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>176800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>171700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>149400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>157500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>168900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>204600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>4</v>
       </c>
@@ -4663,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4893,11 +5061,11 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>1370500</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,65 +5158,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1256500</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>-1292200</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-1269800</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>-902900</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U72" s="3">
         <v>-835500</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>4</v>
       </c>
@@ -5061,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,65 +5466,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" s="3">
         <v>515600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>506200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>514500</v>
       </c>
-      <c r="G76" s="3">
-        <v>502300</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3">
         <v>509100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>523400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>512800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>521400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>557000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>547200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>825200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>835000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>851800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>886500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>920700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>908900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-835200</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>4</v>
       </c>
@@ -5357,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3">
         <v>5900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2500</v>
       </c>
-      <c r="G81" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I81" s="3">
         <v>-12900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-303300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-17400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-22300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-156300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-86700</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-80200</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5644,8 +5843,8 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -5665,8 +5864,8 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>4</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>4</v>
@@ -5686,8 +5885,11 @@
       <c r="Z83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,8 +6270,11 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6088,8 +6305,8 @@
       <c r="L89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -6109,8 +6326,8 @@
       <c r="S89" s="3">
         <v>0</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>4</v>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>4</v>
@@ -6130,8 +6347,11 @@
       <c r="Z89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,8 +6378,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6190,8 +6411,8 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -6211,8 +6432,8 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>4</v>
@@ -6232,8 +6453,11 @@
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,8 +6607,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6412,8 +6642,8 @@
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -6433,8 +6663,8 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>4</v>
@@ -6454,8 +6684,11 @@
       <c r="Z94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6514,8 +6748,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,8 +7021,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6810,8 +7056,8 @@
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -6831,8 +7077,8 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>4</v>
@@ -6852,8 +7098,11 @@
       <c r="Z100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6884,8 +7133,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6905,8 +7154,8 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>4</v>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>4</v>
@@ -6926,8 +7175,11 @@
       <c r="Z101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6952,8 +7204,8 @@
       <c r="J102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -6979,8 +7231,8 @@
       <c r="S102" s="3">
         <v>0</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>4</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>4</v>
@@ -6998,6 +7250,9 @@
         <v>4</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
